--- a/rasch-lite/preview/laporan/contoh_laporan_dikotomus.xlsx
+++ b/rasch-lite/preview/laporan/contoh_laporan_dikotomus.xlsx
@@ -8,14 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Ringkasan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Butir" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Responden" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Item Measures" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Person Measures" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="DIF" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Kontras PCA" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Matriks Q3" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Pasangan Q3" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PCA First Contrast" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Q3 Matrix" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Q3 Flagged Pairs" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Catatan" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Log Iterasi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Iteration Log" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Pengaturan" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
@@ -40,17 +40,20 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001F2F45"/>
       <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="002A2522"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="007A5638"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -59,32 +62,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6E6E6"/>
+        <fgColor rgb="00EEE6DC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBF6C4"/>
+        <fgColor rgb="00F6EAD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BFE6DA"/>
+        <fgColor rgb="00DCE8E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5C9AE"/>
+        <fgColor rgb="00F4DED5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBE3D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F7F3EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -114,14 +112,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -506,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dihasilkan oleh RaschLite by CSPS versi 0.1.0 pada 01-10-2026 17:27</t>
+          <t>Dihasilkan oleh RaschLite by CSPS versi 0.1.0 pada 01-10-2026 18:34</t>
         </is>
       </c>
     </row>
@@ -530,14 +527,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rasch dikotomus</t>
+          <t>Dichotomous Rasch Model</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Responden (dianalisis / ekstrem)</t>
+          <t>Person (diestimasi / extreme score)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -549,7 +546,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Butir (dianalisis / ekstrem)</t>
+          <t>Item (diestimasi / extreme score)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,7 +558,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Data hilang</t>
+          <t>Missing data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -573,7 +570,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Konvergensi</t>
+          <t>Convergence (JMLE)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -585,19 +582,19 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Kriteria konvergensi</t>
+          <t>Convergence criteria</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>perubahan &lt; 0,001 logit dan residual &lt; 0,01</t>
+          <t>max logit change &lt; 0,001 dan max score residual &lt; 0,01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Rentang MNSQ</t>
+          <t>MNSQ fit range</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -609,7 +606,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Faktor koreksi bias (L-1)/L</t>
+          <t>JMLE bias correction (L-1)/L</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -657,7 +654,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Reliabilitas</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -667,14 +664,14 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Konsistensi pengukuran memadai tetapi belum ideal (reliabilitas person 0,77).</t>
+          <t>Konsistensi pengukuran memadai tetapi belum ideal (person reliability 0,77, person separation 1,83).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Kecocokan butir</t>
+          <t>Item Fit</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -684,14 +681,14 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>1 butir berada di luar rentang kecocokan 0,5-1,5 dan perlu diperiksa: S07.</t>
+          <t>1 item berada di luar rentang MNSQ 0,5-1,5 dan perlu diperiksa: S07.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Dimensionalitas</t>
+          <t>Dimensionality</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -701,14 +698,14 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Data mendukung asumsi bahwa tes mengukur satu hal utama (eigenvalue kontras pertama 1,42 &lt; 2,0) tanpa pasangan butir yang saling bergantung.</t>
+          <t>Data mendukung unidimensionality: tes mengukur satu hal utama (first contrast eigenvalue 1,42 &lt; 2,0) tanpa pasangan item yang saling bergantung.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Kesesuaian target</t>
+          <t>Targeting</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -718,14 +715,14 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Tingkat kesulitan butir sesuai dengan kemampuan responden (selisih rata-rata 0,25 logit).</t>
+          <t>Tingkat kesulitan item sesuai dengan kemampuan person (selisih rata-rata measure 0,25 logit).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Fungsi kategori</t>
+          <t>Category Functioning</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -735,7 +732,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Tidak berlaku: data dikotomus hanya memiliki dua kategori.</t>
+          <t>Tidak berlaku: data dichotomous hanya memiliki dua kategori.</t>
         </is>
       </c>
     </row>
@@ -752,14 +749,14 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>1 butir menunjukkan DIF besar antar-kelompok dan perlu ditelaah isinya: S12.</t>
+          <t>1 item menunjukkan DIF besar (ETS category C) dan perlu ditelaah isinya: S12.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Reliabilitas dan Separasi</t>
+          <t>Reliability and Separation</t>
         </is>
       </c>
     </row>
@@ -783,7 +780,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Reliabilitas person (REAL / MODEL)</t>
+          <t>Person reliability (REAL / MODEL)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -800,7 +797,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Separasi person (REAL / MODEL)</t>
+          <t>Person separation (REAL / MODEL)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -817,7 +814,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Strata person</t>
+          <t>Person strata</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -834,7 +831,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Reliabilitas item (REAL / MODEL)</t>
+          <t>Item reliability (REAL / MODEL)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -851,7 +848,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Separasi item (REAL / MODEL)</t>
+          <t>Item separation (REAL / MODEL)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -868,7 +865,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RMSE person (REAL)</t>
+          <t>Person RMSE (REAL)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -881,7 +878,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SD measure person (populasi)</t>
+          <t>Person measure SD (population)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -911,7 +908,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Kecocokan Butir dan Responden</t>
+          <t>Item and Person Fit</t>
         </is>
       </c>
     </row>
@@ -935,7 +932,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rentang MNSQ yang dipakai</t>
+          <t>MNSQ fit range</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -945,14 +942,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>produktif</t>
+          <t>productive for measurement</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Batas MNSQ merusak pengukuran</t>
+          <t>Degrading MNSQ limit</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -969,7 +966,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rerata infit / outfit item</t>
+          <t>Mean item Infit / Outfit MNSQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -986,7 +983,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rerata infit / outfit person</t>
+          <t>Mean person Infit / Outfit MNSQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1003,7 +1000,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Butir di luar rentang</t>
+          <t>Misfitting items</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1020,7 +1017,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Butir dengan point-measure negatif</t>
+          <t>Items with negative PTMEA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1037,7 +1034,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Responden di luar rentang</t>
+          <t>Misfitting persons</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1055,7 +1052,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>infit 1,51 (z 11,1), outfit 1,96 (z 11,7), PTMEA 0,11 / harapan 0,49</t>
+          <t>Infit 1,51 (ZSTD 11,1), Outfit 1,96 (ZSTD 11,7), PTMEA 0,11 / exp. 0,49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1063,7 +1060,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Dimensionalitas dan Dependensi Lokal</t>
+          <t>Dimensionality and Local Dependence</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1084,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Eigenvalue kontras pertama</t>
+          <t>First contrast eigenvalue</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1104,7 +1101,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Varians dijelaskan measure</t>
+          <t>Raw variance explained by measures</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1121,7 +1118,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kontras pertama (% total varians)</t>
+          <t>First contrast (% of total variance)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1134,7 +1131,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rata-rata Q3</t>
+          <t>Mean Q3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1147,7 +1144,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Batas Q3 (rata-rata + 0,2)</t>
+          <t>Q3 cutoff (mean Q3 + 0,2)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1164,7 +1161,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Q3 maksimum</t>
+          <t>Max Q3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1177,7 +1174,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pasangan Q3 ditandai</t>
+          <t>Flagged Q3 pairs</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1194,7 +1191,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Kesesuaian Target</t>
+          <t>Targeting</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1215,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Rerata measure person (non-ekstrem)</t>
+          <t>Mean person measure (non-extreme)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1231,7 +1228,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SD measure person</t>
+          <t>Person measure SD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1244,7 +1241,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Rerata measure item</t>
+          <t>Mean item measure</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1261,7 +1258,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Selisih (targeting)</t>
+          <t>Targeting (mean difference)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1278,7 +1275,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Satuan targeting</t>
+          <t>Targeting unit</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1288,14 +1285,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>yang lebih kecil antara 1 logit dan RMSE person (MODEL); tafsiran teraman tabel Fisher (2007)</t>
+          <t>yang lebih kecil antara 1 logit dan person RMSE (MODEL); tafsiran teraman tabel Fisher (2007)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Person di atas butir tersulit</t>
+          <t>Persons above the hardest item</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1308,7 +1305,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Person di bawah butir termudah</t>
+          <t>Persons below the easiest item</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1321,7 +1318,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Skor ekstrem (maks / min)</t>
+          <t>Extreme scores (maximum / minimum)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1334,7 +1331,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Keadilan Butir antar-Kelompok (DIF)</t>
+          <t>Differential Item Functioning (DIF)</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1355,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kelompok (A / B)</t>
+          <t>Groups (A / B)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1368,31 +1365,31 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>kontras = measure A - measure B</t>
+          <t>DIF contrast = measure A - measure B</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kriteria penanda</t>
+          <t>Flagging criterion</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>kontras mutlak &gt;= 0,5 dan |t| &gt; 2,0</t>
+          <t>DIF contrast mutlak &gt;= 0,5 dan t mutlak &gt; 2,0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Draba (1977): t &gt; 2,0; t &gt; 2,4 bila lebih dari 20 butir</t>
+          <t>Draba (1977): t &gt; 2,0; t &gt; 2,4 bila lebih dari 20 item</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kategori ETS (A / B / C)</t>
+          <t>ETS category (A / B / C)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1414,7 +1411,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1,16 vs 2,13; kontras -0,97 (SE 0,21), t(553) = -4,60, p &lt; 0,001</t>
+          <t>1,16 vs 2,13; DIF contrast -0,97 (Joint SE 0,21), t(553) = -4,60, p &lt; 0,001</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1609,8 +1606,8 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -1620,13 +1617,13 @@
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Butir</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
@@ -1636,12 +1633,12 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Skor</t>
+          <t>Raw Score</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Jumlah respons</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
@@ -1651,7 +1648,7 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>Model SE</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -1676,12 +1673,12 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
-          <t>PTMEA teramati</t>
+          <t>PTMEA Corr. (obs.)</t>
         </is>
       </c>
       <c r="L1" s="4" t="inlineStr">
         <is>
-          <t>PTMEA harapan</t>
+          <t>PTMEA Corr. (exp.)</t>
         </is>
       </c>
       <c r="M1" s="4" t="inlineStr">
@@ -1691,7 +1688,7 @@
       </c>
       <c r="N1" s="4" t="inlineStr">
         <is>
-          <t>PTMEA negatif</t>
+          <t>Negative PTMEA</t>
         </is>
       </c>
     </row>
@@ -1936,48 +1933,48 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>S07</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr"/>
-      <c r="C8" s="12" t="n">
+      <c r="B8" s="8" t="inlineStr"/>
+      <c r="C8" s="11" t="n">
         <v>289</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="8" t="n">
         <v>583</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="12" t="n">
         <v>0.2879676724662681</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="12" t="n">
         <v>0.09088951846800521</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="12" t="n">
         <v>1.513968936616067</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="12" t="n">
         <v>11.07129111139439</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="I8" s="12" t="n">
         <v>1.956314764564844</v>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="12" t="n">
         <v>11.70376427203417</v>
       </c>
-      <c r="K8" s="13" t="n">
+      <c r="K8" s="12" t="n">
         <v>0.1062982853332385</v>
       </c>
-      <c r="L8" s="13" t="n">
+      <c r="L8" s="12" t="n">
         <v>0.4917064976327663</v>
       </c>
-      <c r="M8" s="11" t="inlineStr">
+      <c r="M8" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="N8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2513,12 +2510,12 @@
   <dimension ref="A1:M601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
@@ -2531,12 +2528,12 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Responden</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Grup</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
@@ -2546,17 +2543,17 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Skor</t>
+          <t>Raw Score</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>Skor maks</t>
+          <t>Max Score</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Jumlah respons</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -2566,7 +2563,7 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>Model SE</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
@@ -2760,90 +2757,90 @@
       <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>R0005</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr"/>
-      <c r="D6" s="12" t="n">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E6" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G6" s="13" t="n">
+      <c r="E6" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G6" s="12" t="n">
         <v>1.823704311594337</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="12" t="n">
         <v>0.6257628644297313</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="I6" s="12" t="n">
         <v>1.232093625665087</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="12" t="n">
         <v>0.7818801392287881</v>
       </c>
-      <c r="K6" s="13" t="n">
+      <c r="K6" s="12" t="n">
         <v>2.146467547966557</v>
       </c>
-      <c r="L6" s="13" t="n">
+      <c r="L6" s="12" t="n">
         <v>1.455329450437696</v>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>R0006</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr"/>
-      <c r="D7" s="12" t="n">
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="E7" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G7" s="13" t="n">
+      <c r="E7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G7" s="12" t="n">
         <v>-0.5655280740349017</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="12" t="n">
         <v>0.5301142963227143</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I7" s="12" t="n">
         <v>1.322218005168658</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="12" t="n">
         <v>1.315641611565699</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="12" t="n">
         <v>1.722049894472431</v>
       </c>
-      <c r="L7" s="13" t="n">
+      <c r="L7" s="12" t="n">
         <v>1.705926564148849</v>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -3424,45 +3421,45 @@
       <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>R0021</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr"/>
-      <c r="D22" s="12" t="n">
+      <c r="C22" s="8" t="inlineStr"/>
+      <c r="D22" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E22" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G22" s="13" t="n">
+      <c r="E22" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G22" s="12" t="n">
         <v>2.258651488166693</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="H22" s="12" t="n">
         <v>0.6836617924804415</v>
       </c>
-      <c r="I22" s="13" t="n">
+      <c r="I22" s="12" t="n">
         <v>1.649963633751591</v>
       </c>
-      <c r="J22" s="13" t="n">
+      <c r="J22" s="12" t="n">
         <v>1.535164277631749</v>
       </c>
-      <c r="K22" s="13" t="n">
+      <c r="K22" s="12" t="n">
         <v>5.323275652399546</v>
       </c>
-      <c r="L22" s="13" t="n">
+      <c r="L22" s="12" t="n">
         <v>2.698094267792175</v>
       </c>
-      <c r="M22" s="11" t="inlineStr">
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -3592,45 +3589,45 @@
       <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>R0025</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr"/>
-      <c r="D26" s="12" t="n">
+      <c r="C26" s="8" t="inlineStr"/>
+      <c r="D26" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="E26" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G26" s="13" t="n">
+      <c r="E26" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G26" s="12" t="n">
         <v>2.795636414735082</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="H26" s="12" t="n">
         <v>0.7930629618978372</v>
       </c>
-      <c r="I26" s="13" t="n">
+      <c r="I26" s="12" t="n">
         <v>0.7090352120039245</v>
       </c>
-      <c r="J26" s="13" t="n">
+      <c r="J26" s="12" t="n">
         <v>-0.4514789451422694</v>
       </c>
-      <c r="K26" s="13" t="n">
+      <c r="K26" s="12" t="n">
         <v>0.2963710401233129</v>
       </c>
-      <c r="L26" s="13" t="n">
+      <c r="L26" s="12" t="n">
         <v>-0.3822159792078697</v>
       </c>
-      <c r="M26" s="11" t="inlineStr">
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -3760,90 +3757,90 @@
       <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>R0029</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr"/>
-      <c r="D30" s="12" t="n">
+      <c r="C30" s="8" t="inlineStr"/>
+      <c r="D30" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="E30" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G30" s="13" t="n">
+      <c r="E30" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G30" s="12" t="n">
         <v>0.5261886035768039</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="H30" s="12" t="n">
         <v>0.537933925537473</v>
       </c>
-      <c r="I30" s="13" t="n">
+      <c r="I30" s="12" t="n">
         <v>1.603735560833244</v>
       </c>
-      <c r="J30" s="13" t="n">
+      <c r="J30" s="12" t="n">
         <v>2.148552445826328</v>
       </c>
-      <c r="K30" s="13" t="n">
+      <c r="K30" s="12" t="n">
         <v>1.591177805812318</v>
       </c>
-      <c r="L30" s="13" t="n">
+      <c r="L30" s="12" t="n">
         <v>1.608180866447645</v>
       </c>
-      <c r="M30" s="11" t="inlineStr">
+      <c r="M30" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>R0030</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr"/>
-      <c r="D31" s="12" t="n">
+      <c r="C31" s="8" t="inlineStr"/>
+      <c r="D31" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E31" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G31" s="13" t="n">
+      <c r="E31" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G31" s="12" t="n">
         <v>1.83438499511204</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="12" t="n">
         <v>0.6237713435108156</v>
       </c>
-      <c r="I31" s="13" t="n">
+      <c r="I31" s="12" t="n">
         <v>1.317409364504839</v>
       </c>
-      <c r="J31" s="13" t="n">
+      <c r="J31" s="12" t="n">
         <v>1.000015226378444</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="12" t="n">
         <v>3.055356293622526</v>
       </c>
-      <c r="L31" s="13" t="n">
+      <c r="L31" s="12" t="n">
         <v>2.07038330576942</v>
       </c>
-      <c r="M31" s="11" t="inlineStr">
+      <c r="M31" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -3973,180 +3970,180 @@
       <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>R0034</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr"/>
-      <c r="D35" s="12" t="n">
+      <c r="C35" s="8" t="inlineStr"/>
+      <c r="D35" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="E35" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G35" s="13" t="n">
+      <c r="E35" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G35" s="12" t="n">
         <v>0.263375923455839</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="H35" s="12" t="n">
         <v>0.5270972683902927</v>
       </c>
-      <c r="I35" s="13" t="n">
+      <c r="I35" s="12" t="n">
         <v>1.406323329608076</v>
       </c>
-      <c r="J35" s="13" t="n">
+      <c r="J35" s="12" t="n">
         <v>1.563163644544791</v>
       </c>
-      <c r="K35" s="13" t="n">
+      <c r="K35" s="12" t="n">
         <v>1.596581399117346</v>
       </c>
-      <c r="L35" s="13" t="n">
+      <c r="L35" s="12" t="n">
         <v>1.621823447156292</v>
       </c>
-      <c r="M35" s="11" t="inlineStr">
+      <c r="M35" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>R0035</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr"/>
-      <c r="D36" s="12" t="n">
+      <c r="C36" s="8" t="inlineStr"/>
+      <c r="D36" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F36" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="G36" s="12" t="n">
         <v>2.191962298344245</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="H36" s="12" t="n">
         <v>0.6931547040879459</v>
       </c>
-      <c r="I36" s="13" t="n">
+      <c r="I36" s="12" t="n">
         <v>1.234986445730537</v>
       </c>
-      <c r="J36" s="13" t="n">
+      <c r="J36" s="12" t="n">
         <v>0.7066012770518999</v>
       </c>
-      <c r="K36" s="13" t="n">
+      <c r="K36" s="12" t="n">
         <v>1.979390148694645</v>
       </c>
-      <c r="L36" s="13" t="n">
+      <c r="L36" s="12" t="n">
         <v>1.168646389090069</v>
       </c>
-      <c r="M36" s="11" t="inlineStr">
+      <c r="M36" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>R0036</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr"/>
-      <c r="D37" s="12" t="n">
+      <c r="C37" s="8" t="inlineStr"/>
+      <c r="D37" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="E37" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G37" s="13" t="n">
+      <c r="E37" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G37" s="12" t="n">
         <v>-0.4775931673973712</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="H37" s="12" t="n">
         <v>0.5446961090999008</v>
       </c>
-      <c r="I37" s="13" t="n">
+      <c r="I37" s="12" t="n">
         <v>0.5789394569004674</v>
       </c>
-      <c r="J37" s="13" t="n">
+      <c r="J37" s="12" t="n">
         <v>-1.951803689109063</v>
       </c>
-      <c r="K37" s="13" t="n">
+      <c r="K37" s="12" t="n">
         <v>0.4696918634865112</v>
       </c>
-      <c r="L37" s="13" t="n">
+      <c r="L37" s="12" t="n">
         <v>-1.631222977103655</v>
       </c>
-      <c r="M37" s="11" t="inlineStr">
+      <c r="M37" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>R0037</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr"/>
-      <c r="D38" s="12" t="n">
+      <c r="C38" s="8" t="inlineStr"/>
+      <c r="D38" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="E38" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F38" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G38" s="13" t="n">
+      <c r="E38" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G38" s="12" t="n">
         <v>0.5444335812258353</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="H38" s="12" t="n">
         <v>0.5338858410554059</v>
       </c>
-      <c r="I38" s="13" t="n">
+      <c r="I38" s="12" t="n">
         <v>0.5045119429561051</v>
       </c>
-      <c r="J38" s="13" t="n">
+      <c r="J38" s="12" t="n">
         <v>-2.349702932407293</v>
       </c>
-      <c r="K38" s="13" t="n">
+      <c r="K38" s="12" t="n">
         <v>0.4168164092905916</v>
       </c>
-      <c r="L38" s="13" t="n">
+      <c r="L38" s="12" t="n">
         <v>-1.939633216318067</v>
       </c>
-      <c r="M38" s="11" t="inlineStr">
+      <c r="M38" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -4317,45 +4314,45 @@
       <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>R0042</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr"/>
-      <c r="D43" s="12" t="n">
+      <c r="C43" s="8" t="inlineStr"/>
+      <c r="D43" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="E43" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G43" s="13" t="n">
+      <c r="E43" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G43" s="12" t="n">
         <v>2.795636414735082</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="H43" s="12" t="n">
         <v>0.7930629618978372</v>
       </c>
-      <c r="I43" s="13" t="n">
+      <c r="I43" s="12" t="n">
         <v>1.117014139213371</v>
       </c>
-      <c r="J43" s="13" t="n">
+      <c r="J43" s="12" t="n">
         <v>0.3901156990994358</v>
       </c>
-      <c r="K43" s="13" t="n">
+      <c r="K43" s="12" t="n">
         <v>1.707955085069375</v>
       </c>
-      <c r="L43" s="13" t="n">
+      <c r="L43" s="12" t="n">
         <v>0.8854454124043183</v>
       </c>
-      <c r="M43" s="11" t="inlineStr">
+      <c r="M43" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -4567,45 +4564,45 @@
       <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>R0048</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr"/>
-      <c r="D49" s="12" t="n">
+      <c r="C49" s="8" t="inlineStr"/>
+      <c r="D49" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E49" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F49" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G49" s="13" t="n">
+      <c r="E49" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G49" s="12" t="n">
         <v>-1.787177512424656</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="H49" s="12" t="n">
         <v>0.6237770670345675</v>
       </c>
-      <c r="I49" s="13" t="n">
+      <c r="I49" s="12" t="n">
         <v>1.375170707779535</v>
       </c>
-      <c r="J49" s="13" t="n">
+      <c r="J49" s="12" t="n">
         <v>1.18825243037171</v>
       </c>
-      <c r="K49" s="13" t="n">
+      <c r="K49" s="12" t="n">
         <v>2.371499290193732</v>
       </c>
-      <c r="L49" s="13" t="n">
+      <c r="L49" s="12" t="n">
         <v>1.563314667873429</v>
       </c>
-      <c r="M49" s="11" t="inlineStr">
+      <c r="M49" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -4694,45 +4691,45 @@
       <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>R0051</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr"/>
-      <c r="D52" s="12" t="n">
+      <c r="C52" s="8" t="inlineStr"/>
+      <c r="D52" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E52" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F52" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G52" s="13" t="n">
+      <c r="E52" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G52" s="12" t="n">
         <v>1.83438499511204</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="H52" s="12" t="n">
         <v>0.6237713435108156</v>
       </c>
-      <c r="I52" s="13" t="n">
+      <c r="I52" s="12" t="n">
         <v>1.436509713469946</v>
       </c>
-      <c r="J52" s="13" t="n">
+      <c r="J52" s="12" t="n">
         <v>1.297448126732924</v>
       </c>
-      <c r="K52" s="13" t="n">
+      <c r="K52" s="12" t="n">
         <v>1.790673936411376</v>
       </c>
-      <c r="L52" s="13" t="n">
+      <c r="L52" s="12" t="n">
         <v>1.113657926846381</v>
       </c>
-      <c r="M52" s="11" t="inlineStr">
+      <c r="M52" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -4862,45 +4859,45 @@
       <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>R0055</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C56" s="11" t="inlineStr"/>
-      <c r="D56" s="12" t="n">
+      <c r="C56" s="8" t="inlineStr"/>
+      <c r="D56" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E56" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F56" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G56" s="13" t="n">
+      <c r="E56" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G56" s="12" t="n">
         <v>2.258651488166693</v>
       </c>
-      <c r="H56" s="13" t="n">
+      <c r="H56" s="12" t="n">
         <v>0.6836617924804415</v>
       </c>
-      <c r="I56" s="13" t="n">
+      <c r="I56" s="12" t="n">
         <v>0.7349689277077399</v>
       </c>
-      <c r="J56" s="13" t="n">
+      <c r="J56" s="12" t="n">
         <v>-0.6257987167500069</v>
       </c>
-      <c r="K56" s="13" t="n">
+      <c r="K56" s="12" t="n">
         <v>0.3953013825970998</v>
       </c>
-      <c r="L56" s="13" t="n">
+      <c r="L56" s="12" t="n">
         <v>-0.5379757516436521</v>
       </c>
-      <c r="M56" s="11" t="inlineStr">
+      <c r="M56" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -4948,90 +4945,90 @@
       <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>R0057</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C58" s="11" t="inlineStr"/>
-      <c r="D58" s="12" t="n">
+      <c r="C58" s="8" t="inlineStr"/>
+      <c r="D58" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E58" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F58" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G58" s="13" t="n">
+      <c r="E58" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G58" s="12" t="n">
         <v>-1.704435463141055</v>
       </c>
-      <c r="H58" s="13" t="n">
+      <c r="H58" s="12" t="n">
         <v>0.6287724621965023</v>
       </c>
-      <c r="I58" s="13" t="n">
+      <c r="I58" s="12" t="n">
         <v>1.547558021683949</v>
       </c>
-      <c r="J58" s="13" t="n">
+      <c r="J58" s="12" t="n">
         <v>1.5654031235206</v>
       </c>
-      <c r="K58" s="13" t="n">
+      <c r="K58" s="12" t="n">
         <v>2.935289113435955</v>
       </c>
-      <c r="L58" s="13" t="n">
+      <c r="L58" s="12" t="n">
         <v>1.997724584507651</v>
       </c>
-      <c r="M58" s="11" t="inlineStr">
+      <c r="M58" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>R0058</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C59" s="11" t="inlineStr"/>
-      <c r="D59" s="12" t="n">
+      <c r="C59" s="8" t="inlineStr"/>
+      <c r="D59" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E59" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F59" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G59" s="13" t="n">
+      <c r="E59" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G59" s="12" t="n">
         <v>-0.01259695299819904</v>
       </c>
-      <c r="H59" s="13" t="n">
+      <c r="H59" s="12" t="n">
         <v>0.5242098425849395</v>
       </c>
-      <c r="I59" s="13" t="n">
+      <c r="I59" s="12" t="n">
         <v>1.237160266410896</v>
       </c>
-      <c r="J59" s="13" t="n">
+      <c r="J59" s="12" t="n">
         <v>1.005422484126712</v>
       </c>
-      <c r="K59" s="13" t="n">
+      <c r="K59" s="12" t="n">
         <v>1.652435200334611</v>
       </c>
-      <c r="L59" s="13" t="n">
+      <c r="L59" s="12" t="n">
         <v>1.785984465328494</v>
       </c>
-      <c r="M59" s="11" t="inlineStr">
+      <c r="M59" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -5079,45 +5076,45 @@
       <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>R0060</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C61" s="11" t="inlineStr"/>
-      <c r="D61" s="12" t="n">
+      <c r="C61" s="8" t="inlineStr"/>
+      <c r="D61" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="E61" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F61" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G61" s="13" t="n">
+      <c r="E61" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G61" s="12" t="n">
         <v>0.7174432575663715</v>
       </c>
-      <c r="H61" s="13" t="n">
+      <c r="H61" s="12" t="n">
         <v>0.5599741629058532</v>
       </c>
-      <c r="I61" s="13" t="n">
+      <c r="I61" s="12" t="n">
         <v>1.659667297346576</v>
       </c>
-      <c r="J61" s="13" t="n">
+      <c r="J61" s="12" t="n">
         <v>2.102164982718198</v>
       </c>
-      <c r="K61" s="13" t="n">
+      <c r="K61" s="12" t="n">
         <v>2.031188084348021</v>
       </c>
-      <c r="L61" s="13" t="n">
+      <c r="L61" s="12" t="n">
         <v>2.047845688506162</v>
       </c>
-      <c r="M61" s="11" t="inlineStr">
+      <c r="M61" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -5206,45 +5203,45 @@
       <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="11" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>R0063</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C64" s="11" t="inlineStr"/>
-      <c r="D64" s="12" t="n">
+      <c r="C64" s="8" t="inlineStr"/>
+      <c r="D64" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E64" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F64" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G64" s="13" t="n">
+      <c r="E64" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G64" s="12" t="n">
         <v>1.278272563332163</v>
       </c>
-      <c r="H64" s="13" t="n">
+      <c r="H64" s="12" t="n">
         <v>0.5955820281373561</v>
       </c>
-      <c r="I64" s="13" t="n">
+      <c r="I64" s="12" t="n">
         <v>0.9766467375668081</v>
       </c>
-      <c r="J64" s="13" t="n">
+      <c r="J64" s="12" t="n">
         <v>0.02331612884100434</v>
       </c>
-      <c r="K64" s="13" t="n">
+      <c r="K64" s="12" t="n">
         <v>1.501766458640071</v>
       </c>
-      <c r="L64" s="13" t="n">
+      <c r="L64" s="12" t="n">
         <v>0.9545098204778546</v>
       </c>
-      <c r="M64" s="11" t="inlineStr">
+      <c r="M64" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -5292,135 +5289,135 @@
       <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="11" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>R0065</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr"/>
-      <c r="D66" s="12" t="n">
+      <c r="C66" s="8" t="inlineStr"/>
+      <c r="D66" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E66" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F66" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G66" s="13" t="n">
+      <c r="E66" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F66" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G66" s="12" t="n">
         <v>1.654415178550067</v>
       </c>
-      <c r="H66" s="13" t="n">
+      <c r="H66" s="12" t="n">
         <v>0.6334844119534303</v>
       </c>
-      <c r="I66" s="13" t="n">
+      <c r="I66" s="12" t="n">
         <v>1.17789762775042</v>
       </c>
-      <c r="J66" s="13" t="n">
+      <c r="J66" s="12" t="n">
         <v>0.6128554961263988</v>
       </c>
-      <c r="K66" s="13" t="n">
+      <c r="K66" s="12" t="n">
         <v>1.984114091859998</v>
       </c>
-      <c r="L66" s="13" t="n">
+      <c r="L66" s="12" t="n">
         <v>1.325593528879501</v>
       </c>
-      <c r="M66" s="11" t="inlineStr">
+      <c r="M66" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>R0066</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C67" s="11" t="inlineStr"/>
-      <c r="D67" s="12" t="n">
+      <c r="C67" s="8" t="inlineStr"/>
+      <c r="D67" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E67" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F67" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G67" s="13" t="n">
+      <c r="E67" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G67" s="12" t="n">
         <v>2.133208054788656</v>
       </c>
-      <c r="H67" s="13" t="n">
+      <c r="H67" s="12" t="n">
         <v>0.6951740050452871</v>
       </c>
-      <c r="I67" s="13" t="n">
+      <c r="I67" s="12" t="n">
         <v>0.6278389210775561</v>
       </c>
-      <c r="J67" s="13" t="n">
+      <c r="J67" s="12" t="n">
         <v>-0.9795675015235786</v>
       </c>
-      <c r="K67" s="13" t="n">
+      <c r="K67" s="12" t="n">
         <v>0.3242225462230704</v>
       </c>
-      <c r="L67" s="13" t="n">
+      <c r="L67" s="12" t="n">
         <v>-0.7129607526013459</v>
       </c>
-      <c r="M67" s="11" t="inlineStr">
+      <c r="M67" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>R0067</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr"/>
-      <c r="D68" s="12" t="n">
+      <c r="C68" s="8" t="inlineStr"/>
+      <c r="D68" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E68" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F68" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G68" s="13" t="n">
+      <c r="E68" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G68" s="12" t="n">
         <v>-0.1168619019054963</v>
       </c>
-      <c r="H68" s="13" t="n">
+      <c r="H68" s="12" t="n">
         <v>0.541924895383912</v>
       </c>
-      <c r="I68" s="13" t="n">
+      <c r="I68" s="12" t="n">
         <v>1.372064968342608</v>
       </c>
-      <c r="J68" s="13" t="n">
+      <c r="J68" s="12" t="n">
         <v>1.413545200610448</v>
       </c>
-      <c r="K68" s="13" t="n">
+      <c r="K68" s="12" t="n">
         <v>1.601083565014095</v>
       </c>
-      <c r="L68" s="13" t="n">
+      <c r="L68" s="12" t="n">
         <v>1.592261836792076</v>
       </c>
-      <c r="M68" s="11" t="inlineStr">
+      <c r="M68" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -5550,45 +5547,45 @@
       <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="11" t="inlineStr">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>R0071</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C72" s="11" t="inlineStr"/>
-      <c r="D72" s="12" t="n">
+      <c r="C72" s="8" t="inlineStr"/>
+      <c r="D72" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E72" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F72" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G72" s="13" t="n">
+      <c r="E72" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G72" s="12" t="n">
         <v>-0.9171210860271507</v>
       </c>
-      <c r="H72" s="13" t="n">
+      <c r="H72" s="12" t="n">
         <v>0.5572950148807445</v>
       </c>
-      <c r="I72" s="13" t="n">
+      <c r="I72" s="12" t="n">
         <v>0.6432848270997662</v>
       </c>
-      <c r="J72" s="13" t="n">
+      <c r="J72" s="12" t="n">
         <v>-1.572540297891764</v>
       </c>
-      <c r="K72" s="13" t="n">
+      <c r="K72" s="12" t="n">
         <v>0.4931663066429255</v>
       </c>
-      <c r="L72" s="13" t="n">
+      <c r="L72" s="12" t="n">
         <v>-1.186306193868502</v>
       </c>
-      <c r="M72" s="11" t="inlineStr">
+      <c r="M72" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -6415,45 +6412,45 @@
       <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="11" t="inlineStr">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t>R0092</t>
         </is>
       </c>
-      <c r="B93" s="11" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C93" s="11" t="inlineStr"/>
-      <c r="D93" s="12" t="n">
+      <c r="C93" s="8" t="inlineStr"/>
+      <c r="D93" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E93" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F93" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G93" s="13" t="n">
+      <c r="E93" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F93" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G93" s="12" t="n">
         <v>-2.244923279930266</v>
       </c>
-      <c r="H93" s="13" t="n">
+      <c r="H93" s="12" t="n">
         <v>0.677792449111126</v>
       </c>
-      <c r="I93" s="13" t="n">
+      <c r="I93" s="12" t="n">
         <v>1.318090046873468</v>
       </c>
-      <c r="J93" s="13" t="n">
+      <c r="J93" s="12" t="n">
         <v>0.8725623846906287</v>
       </c>
-      <c r="K93" s="13" t="n">
+      <c r="K93" s="12" t="n">
         <v>2.626665359760265</v>
       </c>
-      <c r="L93" s="13" t="n">
+      <c r="L93" s="12" t="n">
         <v>1.516712900798474</v>
       </c>
-      <c r="M93" s="11" t="inlineStr">
+      <c r="M93" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -6542,45 +6539,45 @@
       <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="11" t="inlineStr">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>R0095</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C96" s="11" t="inlineStr"/>
-      <c r="D96" s="12" t="n">
+      <c r="C96" s="8" t="inlineStr"/>
+      <c r="D96" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E96" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F96" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G96" s="13" t="n">
+      <c r="E96" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F96" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G96" s="12" t="n">
         <v>-1.095431413484603</v>
       </c>
-      <c r="H96" s="13" t="n">
+      <c r="H96" s="12" t="n">
         <v>0.5651149143913906</v>
       </c>
-      <c r="I96" s="13" t="n">
+      <c r="I96" s="12" t="n">
         <v>1.43921572895896</v>
       </c>
-      <c r="J96" s="13" t="n">
+      <c r="J96" s="12" t="n">
         <v>1.619556089561519</v>
       </c>
-      <c r="K96" s="13" t="n">
+      <c r="K96" s="12" t="n">
         <v>2.046868509564084</v>
       </c>
-      <c r="L96" s="13" t="n">
+      <c r="L96" s="12" t="n">
         <v>1.739083985651215</v>
       </c>
-      <c r="M96" s="11" t="inlineStr">
+      <c r="M96" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -6628,45 +6625,45 @@
       <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="11" t="inlineStr">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>R0097</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C98" s="11" t="inlineStr"/>
-      <c r="D98" s="12" t="n">
+      <c r="C98" s="8" t="inlineStr"/>
+      <c r="D98" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E98" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F98" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G98" s="13" t="n">
+      <c r="E98" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F98" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G98" s="12" t="n">
         <v>-1.402740447811646</v>
       </c>
-      <c r="H98" s="13" t="n">
+      <c r="H98" s="12" t="n">
         <v>0.5901846181794939</v>
       </c>
-      <c r="I98" s="13" t="n">
+      <c r="I98" s="12" t="n">
         <v>1.163211335268928</v>
       </c>
-      <c r="J98" s="13" t="n">
+      <c r="J98" s="12" t="n">
         <v>0.654874938266876</v>
       </c>
-      <c r="K98" s="13" t="n">
+      <c r="K98" s="12" t="n">
         <v>1.62413787905533</v>
       </c>
-      <c r="L98" s="13" t="n">
+      <c r="L98" s="12" t="n">
         <v>1.056282999483027</v>
       </c>
-      <c r="M98" s="11" t="inlineStr">
+      <c r="M98" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -6714,45 +6711,45 @@
       <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="11" t="inlineStr">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>R0099</t>
         </is>
       </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C100" s="11" t="inlineStr"/>
-      <c r="D100" s="12" t="n">
+      <c r="C100" s="8" t="inlineStr"/>
+      <c r="D100" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E100" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F100" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G100" s="13" t="n">
+      <c r="E100" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F100" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G100" s="12" t="n">
         <v>1.46967040698167</v>
       </c>
-      <c r="H100" s="13" t="n">
+      <c r="H100" s="12" t="n">
         <v>0.5865582715673844</v>
       </c>
-      <c r="I100" s="13" t="n">
+      <c r="I100" s="12" t="n">
         <v>0.6607827916806049</v>
       </c>
-      <c r="J100" s="13" t="n">
+      <c r="J100" s="12" t="n">
         <v>-1.232039391238074</v>
       </c>
-      <c r="K100" s="13" t="n">
+      <c r="K100" s="12" t="n">
         <v>0.4759409601952488</v>
       </c>
-      <c r="L100" s="13" t="n">
+      <c r="L100" s="12" t="n">
         <v>-0.8880507845761303</v>
       </c>
-      <c r="M100" s="11" t="inlineStr">
+      <c r="M100" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -7087,45 +7084,45 @@
       <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="11" t="inlineStr">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>R0108</t>
         </is>
       </c>
-      <c r="B109" s="11" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C109" s="11" t="inlineStr"/>
-      <c r="D109" s="12" t="n">
+      <c r="C109" s="8" t="inlineStr"/>
+      <c r="D109" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E109" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F109" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G109" s="13" t="n">
+      <c r="E109" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F109" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G109" s="12" t="n">
         <v>1.140817678674626</v>
       </c>
-      <c r="H109" s="13" t="n">
+      <c r="H109" s="12" t="n">
         <v>0.5618791360218677</v>
       </c>
-      <c r="I109" s="13" t="n">
+      <c r="I109" s="12" t="n">
         <v>0.9413981618190335</v>
       </c>
-      <c r="J109" s="13" t="n">
+      <c r="J109" s="12" t="n">
         <v>-0.1279309887103137</v>
       </c>
-      <c r="K109" s="13" t="n">
+      <c r="K109" s="12" t="n">
         <v>1.830056587032515</v>
       </c>
-      <c r="L109" s="13" t="n">
+      <c r="L109" s="12" t="n">
         <v>1.504483649291756</v>
       </c>
-      <c r="M109" s="11" t="inlineStr">
+      <c r="M109" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -7173,45 +7170,45 @@
       <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="11" t="inlineStr">
+      <c r="A111" s="8" t="inlineStr">
         <is>
           <t>R0110</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C111" s="11" t="inlineStr"/>
-      <c r="D111" s="12" t="n">
+      <c r="C111" s="8" t="inlineStr"/>
+      <c r="D111" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E111" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F111" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G111" s="13" t="n">
+      <c r="E111" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F111" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G111" s="12" t="n">
         <v>1.83438499511204</v>
       </c>
-      <c r="H111" s="13" t="n">
+      <c r="H111" s="12" t="n">
         <v>0.6237713435108156</v>
       </c>
-      <c r="I111" s="13" t="n">
+      <c r="I111" s="12" t="n">
         <v>0.6344028905126842</v>
       </c>
-      <c r="J111" s="13" t="n">
+      <c r="J111" s="12" t="n">
         <v>-1.196776162592294</v>
       </c>
-      <c r="K111" s="13" t="n">
+      <c r="K111" s="12" t="n">
         <v>0.381221712793226</v>
       </c>
-      <c r="L111" s="13" t="n">
+      <c r="L111" s="12" t="n">
         <v>-0.8635819447375632</v>
       </c>
-      <c r="M111" s="11" t="inlineStr">
+      <c r="M111" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -7464,45 +7461,45 @@
       <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="11" t="inlineStr">
+      <c r="A118" s="8" t="inlineStr">
         <is>
           <t>R0117</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C118" s="11" t="inlineStr"/>
-      <c r="D118" s="12" t="n">
+      <c r="C118" s="8" t="inlineStr"/>
+      <c r="D118" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="E118" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F118" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G118" s="13" t="n">
+      <c r="E118" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F118" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G118" s="12" t="n">
         <v>0.8350494176261472</v>
       </c>
-      <c r="H118" s="13" t="n">
+      <c r="H118" s="12" t="n">
         <v>0.5450927213778975</v>
       </c>
-      <c r="I118" s="13" t="n">
+      <c r="I118" s="12" t="n">
         <v>1.120594073247157</v>
       </c>
-      <c r="J118" s="13" t="n">
+      <c r="J118" s="12" t="n">
         <v>0.5317223721492896</v>
       </c>
-      <c r="K118" s="13" t="n">
+      <c r="K118" s="12" t="n">
         <v>1.722614661587046</v>
       </c>
-      <c r="L118" s="13" t="n">
+      <c r="L118" s="12" t="n">
         <v>1.550342970407338</v>
       </c>
-      <c r="M118" s="11" t="inlineStr">
+      <c r="M118" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -7591,90 +7588,90 @@
       <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="11" t="inlineStr">
+      <c r="A121" s="8" t="inlineStr">
         <is>
           <t>R0120</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr">
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C121" s="11" t="inlineStr"/>
-      <c r="D121" s="12" t="n">
+      <c r="C121" s="8" t="inlineStr"/>
+      <c r="D121" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E121" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F121" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G121" s="13" t="n">
+      <c r="E121" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F121" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G121" s="12" t="n">
         <v>1.46967040698167</v>
       </c>
-      <c r="H121" s="13" t="n">
+      <c r="H121" s="12" t="n">
         <v>0.5865582715673844</v>
       </c>
-      <c r="I121" s="13" t="n">
+      <c r="I121" s="12" t="n">
         <v>0.7094221422579345</v>
       </c>
-      <c r="J121" s="13" t="n">
+      <c r="J121" s="12" t="n">
         <v>-1.017038452890817</v>
       </c>
-      <c r="K121" s="13" t="n">
+      <c r="K121" s="12" t="n">
         <v>0.4935410923991634</v>
       </c>
-      <c r="L121" s="13" t="n">
+      <c r="L121" s="12" t="n">
         <v>-0.8408101850539904</v>
       </c>
-      <c r="M121" s="11" t="inlineStr">
+      <c r="M121" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="11" t="inlineStr">
+      <c r="A122" s="8" t="inlineStr">
         <is>
           <t>R0121</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B122" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C122" s="11" t="inlineStr"/>
-      <c r="D122" s="12" t="n">
+      <c r="C122" s="8" t="inlineStr"/>
+      <c r="D122" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E122" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F122" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G122" s="13" t="n">
+      <c r="E122" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F122" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G122" s="12" t="n">
         <v>-0.287528625922924</v>
       </c>
-      <c r="H122" s="13" t="n">
+      <c r="H122" s="12" t="n">
         <v>0.525128174663108</v>
       </c>
-      <c r="I122" s="13" t="n">
+      <c r="I122" s="12" t="n">
         <v>0.586509178768485</v>
       </c>
-      <c r="J122" s="13" t="n">
+      <c r="J122" s="12" t="n">
         <v>-1.996459526935994</v>
       </c>
-      <c r="K122" s="13" t="n">
+      <c r="K122" s="12" t="n">
         <v>0.4892455326124145</v>
       </c>
-      <c r="L122" s="13" t="n">
+      <c r="L122" s="12" t="n">
         <v>-1.755697643685374</v>
       </c>
-      <c r="M122" s="11" t="inlineStr">
+      <c r="M122" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -7968,45 +7965,45 @@
       <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="11" t="inlineStr">
+      <c r="A130" s="8" t="inlineStr">
         <is>
           <t>R0129</t>
         </is>
       </c>
-      <c r="B130" s="11" t="inlineStr">
+      <c r="B130" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C130" s="11" t="inlineStr"/>
-      <c r="D130" s="12" t="n">
+      <c r="C130" s="8" t="inlineStr"/>
+      <c r="D130" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="E130" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F130" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G130" s="13" t="n">
+      <c r="E130" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F130" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G130" s="12" t="n">
         <v>-0.342159383262933</v>
       </c>
-      <c r="H130" s="13" t="n">
+      <c r="H130" s="12" t="n">
         <v>0.5377055572393262</v>
       </c>
-      <c r="I130" s="13" t="n">
+      <c r="I130" s="12" t="n">
         <v>0.595653745299457</v>
       </c>
-      <c r="J130" s="13" t="n">
+      <c r="J130" s="12" t="n">
         <v>-1.935436541483604</v>
       </c>
-      <c r="K130" s="13" t="n">
+      <c r="K130" s="12" t="n">
         <v>0.4925190250847013</v>
       </c>
-      <c r="L130" s="13" t="n">
+      <c r="L130" s="12" t="n">
         <v>-1.657528488262909</v>
       </c>
-      <c r="M130" s="11" t="inlineStr">
+      <c r="M130" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -8054,45 +8051,45 @@
       <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="11" t="inlineStr">
+      <c r="A132" s="8" t="inlineStr">
         <is>
           <t>R0131</t>
         </is>
       </c>
-      <c r="B132" s="11" t="inlineStr">
+      <c r="B132" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C132" s="11" t="inlineStr"/>
-      <c r="D132" s="12" t="n">
+      <c r="C132" s="8" t="inlineStr"/>
+      <c r="D132" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E132" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F132" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G132" s="13" t="n">
+      <c r="E132" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F132" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G132" s="12" t="n">
         <v>-1.828758139764982</v>
       </c>
-      <c r="H132" s="13" t="n">
+      <c r="H132" s="12" t="n">
         <v>0.6172109748082045</v>
       </c>
-      <c r="I132" s="13" t="n">
+      <c r="I132" s="12" t="n">
         <v>1.367117760004184</v>
       </c>
-      <c r="J132" s="13" t="n">
+      <c r="J132" s="12" t="n">
         <v>1.143247404331568</v>
       </c>
-      <c r="K132" s="13" t="n">
+      <c r="K132" s="12" t="n">
         <v>1.790376244090388</v>
       </c>
-      <c r="L132" s="13" t="n">
+      <c r="L132" s="12" t="n">
         <v>1.103445379035704</v>
       </c>
-      <c r="M132" s="11" t="inlineStr">
+      <c r="M132" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -8263,131 +8260,131 @@
       <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="11" t="inlineStr">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>R0136</t>
         </is>
       </c>
-      <c r="B137" s="11" t="inlineStr">
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C137" s="11" t="inlineStr"/>
-      <c r="D137" s="12" t="n">
+      <c r="C137" s="8" t="inlineStr"/>
+      <c r="D137" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E137" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F137" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G137" s="13" t="n">
+      <c r="E137" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F137" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G137" s="12" t="n">
         <v>2.258651488166693</v>
       </c>
-      <c r="H137" s="13" t="n">
+      <c r="H137" s="12" t="n">
         <v>0.6836617924804415</v>
       </c>
-      <c r="I137" s="13" t="n">
+      <c r="I137" s="12" t="n">
         <v>0.7349689277077399</v>
       </c>
-      <c r="J137" s="13" t="n">
+      <c r="J137" s="12" t="n">
         <v>-0.6257987167500069</v>
       </c>
-      <c r="K137" s="13" t="n">
+      <c r="K137" s="12" t="n">
         <v>0.3953013825970998</v>
       </c>
-      <c r="L137" s="13" t="n">
+      <c r="L137" s="12" t="n">
         <v>-0.5379757516436521</v>
       </c>
-      <c r="M137" s="11" t="inlineStr">
+      <c r="M137" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="11" t="inlineStr">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>R0137</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C138" s="11" t="inlineStr"/>
-      <c r="D138" s="12" t="n">
+      <c r="C138" s="8" t="inlineStr"/>
+      <c r="D138" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E138" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F138" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G138" s="13" t="n">
+      <c r="E138" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F138" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G138" s="12" t="n">
         <v>1.140817678674626</v>
       </c>
-      <c r="H138" s="13" t="n">
+      <c r="H138" s="12" t="n">
         <v>0.5618791360218677</v>
       </c>
-      <c r="I138" s="13" t="n">
+      <c r="I138" s="12" t="n">
         <v>0.6446811292510435</v>
       </c>
-      <c r="J138" s="13" t="n">
+      <c r="J138" s="12" t="n">
         <v>-1.404613271489486</v>
       </c>
-      <c r="K138" s="13" t="n">
+      <c r="K138" s="12" t="n">
         <v>0.482929907916255</v>
       </c>
-      <c r="L138" s="13" t="n">
+      <c r="L138" s="12" t="n">
         <v>-1.12442676947868</v>
       </c>
-      <c r="M138" s="11" t="inlineStr">
+      <c r="M138" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="14" t="inlineStr">
+      <c r="A139" s="13" t="inlineStr">
         <is>
           <t>R0138</t>
         </is>
       </c>
-      <c r="B139" s="14" t="inlineStr">
+      <c r="B139" s="13" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C139" s="14" t="inlineStr">
-        <is>
-          <t>ekstrem maksimum</t>
-        </is>
-      </c>
-      <c r="D139" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="E139" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="F139" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="G139" s="16" t="n">
+      <c r="C139" s="13" t="inlineStr">
+        <is>
+          <t>Extreme (maximum)</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="E139" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="F139" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="G139" s="15" t="n">
         <v>4.869734739943151</v>
       </c>
-      <c r="H139" s="16" t="n">
+      <c r="H139" s="15" t="n">
         <v>1.860371986437237</v>
       </c>
-      <c r="I139" s="14" t="n"/>
-      <c r="J139" s="14" t="n"/>
-      <c r="K139" s="14" t="n"/>
-      <c r="L139" s="14" t="n"/>
-      <c r="M139" s="14" t="inlineStr"/>
+      <c r="I139" s="13" t="n"/>
+      <c r="J139" s="13" t="n"/>
+      <c r="K139" s="13" t="n"/>
+      <c r="L139" s="13" t="n"/>
+      <c r="M139" s="13" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8800,45 +8797,45 @@
       <c r="M149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="11" t="inlineStr">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t>R0149</t>
         </is>
       </c>
-      <c r="B150" s="11" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C150" s="11" t="inlineStr"/>
-      <c r="D150" s="12" t="n">
+      <c r="C150" s="8" t="inlineStr"/>
+      <c r="D150" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E150" s="11" t="n">
+      <c r="E150" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F150" s="11" t="n">
+      <c r="F150" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="G150" s="13" t="n">
+      <c r="G150" s="12" t="n">
         <v>2.586852738362467</v>
       </c>
-      <c r="H150" s="13" t="n">
+      <c r="H150" s="12" t="n">
         <v>0.8020148714902673</v>
       </c>
-      <c r="I150" s="13" t="n">
+      <c r="I150" s="12" t="n">
         <v>0.7092967361928381</v>
       </c>
-      <c r="J150" s="13" t="n">
+      <c r="J150" s="12" t="n">
         <v>-0.4584397696559285</v>
       </c>
-      <c r="K150" s="13" t="n">
+      <c r="K150" s="12" t="n">
         <v>0.3239648733549659</v>
       </c>
-      <c r="L150" s="13" t="n">
+      <c r="L150" s="12" t="n">
         <v>-0.3859540041955454</v>
       </c>
-      <c r="M150" s="11" t="inlineStr">
+      <c r="M150" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -9173,45 +9170,45 @@
       <c r="M158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="11" t="inlineStr">
+      <c r="A159" s="8" t="inlineStr">
         <is>
           <t>R0158</t>
         </is>
       </c>
-      <c r="B159" s="11" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C159" s="11" t="inlineStr"/>
-      <c r="D159" s="12" t="n">
+      <c r="C159" s="8" t="inlineStr"/>
+      <c r="D159" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="E159" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F159" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G159" s="13" t="n">
+      <c r="E159" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F159" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G159" s="12" t="n">
         <v>0.7174432575663716</v>
       </c>
-      <c r="H159" s="13" t="n">
+      <c r="H159" s="12" t="n">
         <v>0.5599741629058532</v>
       </c>
-      <c r="I159" s="13" t="n">
+      <c r="I159" s="12" t="n">
         <v>1.518772035830172</v>
       </c>
-      <c r="J159" s="13" t="n">
+      <c r="J159" s="12" t="n">
         <v>1.725108499238626</v>
       </c>
-      <c r="K159" s="13" t="n">
+      <c r="K159" s="12" t="n">
         <v>1.936645351167116</v>
       </c>
-      <c r="L159" s="13" t="n">
+      <c r="L159" s="12" t="n">
         <v>1.904877788622044</v>
       </c>
-      <c r="M159" s="11" t="inlineStr">
+      <c r="M159" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -9382,45 +9379,45 @@
       <c r="M163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="11" t="inlineStr">
+      <c r="A164" s="8" t="inlineStr">
         <is>
           <t>R0163</t>
         </is>
       </c>
-      <c r="B164" s="11" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C164" s="11" t="inlineStr"/>
-      <c r="D164" s="12" t="n">
+      <c r="C164" s="8" t="inlineStr"/>
+      <c r="D164" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E164" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F164" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G164" s="13" t="n">
+      <c r="E164" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F164" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G164" s="12" t="n">
         <v>1.46967040698167</v>
       </c>
-      <c r="H164" s="13" t="n">
+      <c r="H164" s="12" t="n">
         <v>0.5865582715673844</v>
       </c>
-      <c r="I164" s="13" t="n">
+      <c r="I164" s="12" t="n">
         <v>0.7975396720048579</v>
       </c>
-      <c r="J164" s="13" t="n">
+      <c r="J164" s="12" t="n">
         <v>-0.651322094599428</v>
       </c>
-      <c r="K164" s="13" t="n">
+      <c r="K164" s="12" t="n">
         <v>1.569793486564287</v>
       </c>
-      <c r="L164" s="13" t="n">
+      <c r="L164" s="12" t="n">
         <v>1.00717050189609</v>
       </c>
-      <c r="M164" s="11" t="inlineStr">
+      <c r="M164" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -9468,45 +9465,45 @@
       <c r="M165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="11" t="inlineStr">
+      <c r="A166" s="8" t="inlineStr">
         <is>
           <t>R0165</t>
         </is>
       </c>
-      <c r="B166" s="11" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C166" s="11" t="inlineStr"/>
-      <c r="D166" s="12" t="n">
+      <c r="C166" s="8" t="inlineStr"/>
+      <c r="D166" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E166" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F166" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G166" s="13" t="n">
+      <c r="E166" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F166" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G166" s="12" t="n">
         <v>2.258651488166693</v>
       </c>
-      <c r="H166" s="13" t="n">
+      <c r="H166" s="12" t="n">
         <v>0.6836617924804415</v>
       </c>
-      <c r="I166" s="13" t="n">
+      <c r="I166" s="12" t="n">
         <v>0.9240937804160722</v>
       </c>
-      <c r="J166" s="13" t="n">
+      <c r="J166" s="12" t="n">
         <v>-0.07179872419574471</v>
       </c>
-      <c r="K166" s="13" t="n">
+      <c r="K166" s="12" t="n">
         <v>0.4882872693204756</v>
       </c>
-      <c r="L166" s="13" t="n">
+      <c r="L166" s="12" t="n">
         <v>-0.3667841400154963</v>
       </c>
-      <c r="M166" s="11" t="inlineStr">
+      <c r="M166" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -9677,45 +9674,45 @@
       <c r="M170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="11" t="inlineStr">
+      <c r="A171" s="8" t="inlineStr">
         <is>
           <t>R0170</t>
         </is>
       </c>
-      <c r="B171" s="11" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C171" s="11" t="inlineStr"/>
-      <c r="D171" s="12" t="n">
+      <c r="C171" s="8" t="inlineStr"/>
+      <c r="D171" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E171" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F171" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G171" s="13" t="n">
+      <c r="E171" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F171" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G171" s="12" t="n">
         <v>1.83438499511204</v>
       </c>
-      <c r="H171" s="13" t="n">
+      <c r="H171" s="12" t="n">
         <v>0.6237713435108156</v>
       </c>
-      <c r="I171" s="13" t="n">
+      <c r="I171" s="12" t="n">
         <v>0.6344028905126842</v>
       </c>
-      <c r="J171" s="13" t="n">
+      <c r="J171" s="12" t="n">
         <v>-1.196776162592294</v>
       </c>
-      <c r="K171" s="13" t="n">
+      <c r="K171" s="12" t="n">
         <v>0.381221712793226</v>
       </c>
-      <c r="L171" s="13" t="n">
+      <c r="L171" s="12" t="n">
         <v>-0.8635819447375632</v>
       </c>
-      <c r="M171" s="11" t="inlineStr">
+      <c r="M171" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -10132,45 +10129,45 @@
       <c r="M181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="11" t="inlineStr">
+      <c r="A182" s="8" t="inlineStr">
         <is>
           <t>R0181</t>
         </is>
       </c>
-      <c r="B182" s="11" t="inlineStr">
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C182" s="11" t="inlineStr"/>
-      <c r="D182" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="E182" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F182" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G182" s="13" t="n">
+      <c r="C182" s="8" t="inlineStr"/>
+      <c r="D182" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E182" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F182" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G182" s="12" t="n">
         <v>3.615189318951955</v>
       </c>
-      <c r="H182" s="13" t="n">
+      <c r="H182" s="12" t="n">
         <v>1.060092004736789</v>
       </c>
-      <c r="I182" s="13" t="n">
+      <c r="I182" s="12" t="n">
         <v>0.8057125452294475</v>
       </c>
-      <c r="J182" s="13" t="n">
+      <c r="J182" s="12" t="n">
         <v>0.03480898434024698</v>
       </c>
-      <c r="K182" s="13" t="n">
+      <c r="K182" s="12" t="n">
         <v>0.2484984232216352</v>
       </c>
-      <c r="L182" s="13" t="n">
+      <c r="L182" s="12" t="n">
         <v>0.0566261312556855</v>
       </c>
-      <c r="M182" s="11" t="inlineStr">
+      <c r="M182" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -10300,135 +10297,135 @@
       <c r="M185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="11" t="inlineStr">
+      <c r="A186" s="8" t="inlineStr">
         <is>
           <t>R0185</t>
         </is>
       </c>
-      <c r="B186" s="11" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C186" s="11" t="inlineStr"/>
-      <c r="D186" s="12" t="n">
+      <c r="C186" s="8" t="inlineStr"/>
+      <c r="D186" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E186" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F186" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G186" s="13" t="n">
+      <c r="E186" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F186" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G186" s="12" t="n">
         <v>2.258651488166693</v>
       </c>
-      <c r="H186" s="13" t="n">
+      <c r="H186" s="12" t="n">
         <v>0.6836617924804415</v>
       </c>
-      <c r="I186" s="13" t="n">
+      <c r="I186" s="12" t="n">
         <v>0.7791415724551213</v>
       </c>
-      <c r="J186" s="13" t="n">
+      <c r="J186" s="12" t="n">
         <v>-0.488583380751537</v>
       </c>
-      <c r="K186" s="13" t="n">
+      <c r="K186" s="12" t="n">
         <v>0.4112935996725181</v>
       </c>
-      <c r="L186" s="13" t="n">
+      <c r="L186" s="12" t="n">
         <v>-0.5067503862426506</v>
       </c>
-      <c r="M186" s="11" t="inlineStr">
+      <c r="M186" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="11" t="inlineStr">
+      <c r="A187" s="8" t="inlineStr">
         <is>
           <t>R0186</t>
         </is>
       </c>
-      <c r="B187" s="11" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C187" s="11" t="inlineStr"/>
-      <c r="D187" s="12" t="n">
+      <c r="C187" s="8" t="inlineStr"/>
+      <c r="D187" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E187" s="11" t="n">
+      <c r="E187" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F187" s="11" t="n">
+      <c r="F187" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="G187" s="13" t="n">
+      <c r="G187" s="12" t="n">
         <v>-1.020556464314256</v>
       </c>
-      <c r="H187" s="13" t="n">
+      <c r="H187" s="12" t="n">
         <v>0.5740137265362527</v>
       </c>
-      <c r="I187" s="13" t="n">
+      <c r="I187" s="12" t="n">
         <v>0.5752509071592337</v>
       </c>
-      <c r="J187" s="13" t="n">
+      <c r="J187" s="12" t="n">
         <v>-1.861501562392715</v>
       </c>
-      <c r="K187" s="13" t="n">
+      <c r="K187" s="12" t="n">
         <v>0.444677645371582</v>
       </c>
-      <c r="L187" s="13" t="n">
+      <c r="L187" s="12" t="n">
         <v>-1.270664398858398</v>
       </c>
-      <c r="M187" s="11" t="inlineStr">
+      <c r="M187" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="11" t="inlineStr">
+      <c r="A188" s="8" t="inlineStr">
         <is>
           <t>R0187</t>
         </is>
       </c>
-      <c r="B188" s="11" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C188" s="11" t="inlineStr"/>
-      <c r="D188" s="12" t="n">
+      <c r="C188" s="8" t="inlineStr"/>
+      <c r="D188" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E188" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F188" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G188" s="13" t="n">
+      <c r="E188" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F188" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G188" s="12" t="n">
         <v>-0.01259695299819895</v>
       </c>
-      <c r="H188" s="13" t="n">
+      <c r="H188" s="12" t="n">
         <v>0.5242098425849395</v>
       </c>
-      <c r="I188" s="13" t="n">
+      <c r="I188" s="12" t="n">
         <v>1.377534359254933</v>
       </c>
-      <c r="J188" s="13" t="n">
+      <c r="J188" s="12" t="n">
         <v>1.498649635559582</v>
       </c>
-      <c r="K188" s="13" t="n">
+      <c r="K188" s="12" t="n">
         <v>1.644142636208459</v>
       </c>
-      <c r="L188" s="13" t="n">
+      <c r="L188" s="12" t="n">
         <v>1.76775230042056</v>
       </c>
-      <c r="M188" s="11" t="inlineStr">
+      <c r="M188" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -10599,45 +10596,45 @@
       <c r="M192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="11" t="inlineStr">
+      <c r="A193" s="8" t="inlineStr">
         <is>
           <t>R0192</t>
         </is>
       </c>
-      <c r="B193" s="11" t="inlineStr">
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C193" s="11" t="inlineStr"/>
-      <c r="D193" s="12" t="n">
+      <c r="C193" s="8" t="inlineStr"/>
+      <c r="D193" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E193" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F193" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G193" s="13" t="n">
+      <c r="E193" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F193" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G193" s="12" t="n">
         <v>-1.828758139764982</v>
       </c>
-      <c r="H193" s="13" t="n">
+      <c r="H193" s="12" t="n">
         <v>0.6172109748082045</v>
       </c>
-      <c r="I193" s="13" t="n">
+      <c r="I193" s="12" t="n">
         <v>1.421524892610002</v>
       </c>
-      <c r="J193" s="13" t="n">
+      <c r="J193" s="12" t="n">
         <v>1.280462134308801</v>
       </c>
-      <c r="K193" s="13" t="n">
+      <c r="K193" s="12" t="n">
         <v>2.771452584983365</v>
       </c>
-      <c r="L193" s="13" t="n">
+      <c r="L193" s="12" t="n">
         <v>1.860420442192688</v>
       </c>
-      <c r="M193" s="11" t="inlineStr">
+      <c r="M193" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -11013,45 +11010,45 @@
       <c r="M202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="11" t="inlineStr">
+      <c r="A203" s="8" t="inlineStr">
         <is>
           <t>R0202</t>
         </is>
       </c>
-      <c r="B203" s="11" t="inlineStr">
+      <c r="B203" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C203" s="11" t="inlineStr"/>
-      <c r="D203" s="12" t="n">
+      <c r="C203" s="8" t="inlineStr"/>
+      <c r="D203" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E203" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F203" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G203" s="13" t="n">
+      <c r="E203" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F203" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G203" s="12" t="n">
         <v>-1.47206402952562</v>
       </c>
-      <c r="H203" s="13" t="n">
+      <c r="H203" s="12" t="n">
         <v>0.5798549876787141</v>
       </c>
-      <c r="I203" s="13" t="n">
+      <c r="I203" s="12" t="n">
         <v>0.908000259558835</v>
       </c>
-      <c r="J203" s="13" t="n">
+      <c r="J203" s="12" t="n">
         <v>-0.2494408720195689</v>
       </c>
-      <c r="K203" s="13" t="n">
+      <c r="K203" s="12" t="n">
         <v>2.384124178324658</v>
       </c>
-      <c r="L203" s="13" t="n">
+      <c r="L203" s="12" t="n">
         <v>1.839548112718864</v>
       </c>
-      <c r="M203" s="11" t="inlineStr">
+      <c r="M203" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -11140,45 +11137,45 @@
       <c r="M205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="11" t="inlineStr">
+      <c r="A206" s="8" t="inlineStr">
         <is>
           <t>R0205</t>
         </is>
       </c>
-      <c r="B206" s="11" t="inlineStr">
+      <c r="B206" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C206" s="11" t="inlineStr"/>
-      <c r="D206" s="12" t="n">
+      <c r="C206" s="8" t="inlineStr"/>
+      <c r="D206" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="E206" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F206" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G206" s="13" t="n">
+      <c r="E206" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F206" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G206" s="12" t="n">
         <v>0.8350494176261472</v>
       </c>
-      <c r="H206" s="13" t="n">
+      <c r="H206" s="12" t="n">
         <v>0.5450927213778975</v>
       </c>
-      <c r="I206" s="13" t="n">
+      <c r="I206" s="12" t="n">
         <v>0.6287674420146144</v>
       </c>
-      <c r="J206" s="13" t="n">
+      <c r="J206" s="12" t="n">
         <v>-1.560568723877034</v>
       </c>
-      <c r="K206" s="13" t="n">
+      <c r="K206" s="12" t="n">
         <v>0.4933324018393357</v>
       </c>
-      <c r="L206" s="13" t="n">
+      <c r="L206" s="12" t="n">
         <v>-1.346934105999915</v>
       </c>
-      <c r="M206" s="11" t="inlineStr">
+      <c r="M206" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -11226,45 +11223,45 @@
       <c r="M207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="11" t="inlineStr">
+      <c r="A208" s="8" t="inlineStr">
         <is>
           <t>R0207</t>
         </is>
       </c>
-      <c r="B208" s="11" t="inlineStr">
+      <c r="B208" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C208" s="11" t="inlineStr"/>
-      <c r="D208" s="12" t="n">
+      <c r="C208" s="8" t="inlineStr"/>
+      <c r="D208" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="E208" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F208" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G208" s="13" t="n">
+      <c r="E208" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F208" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G208" s="12" t="n">
         <v>3.433688462399699</v>
       </c>
-      <c r="H208" s="13" t="n">
+      <c r="H208" s="12" t="n">
         <v>1.065826628143488</v>
       </c>
-      <c r="I208" s="13" t="n">
+      <c r="I208" s="12" t="n">
         <v>0.9408250328468335</v>
       </c>
-      <c r="J208" s="13" t="n">
+      <c r="J208" s="12" t="n">
         <v>0.2068528544680668</v>
       </c>
-      <c r="K208" s="13" t="n">
+      <c r="K208" s="12" t="n">
         <v>0.3596251045202771</v>
       </c>
-      <c r="L208" s="13" t="n">
+      <c r="L208" s="12" t="n">
         <v>0.1387685497081027</v>
       </c>
-      <c r="M208" s="11" t="inlineStr">
+      <c r="M208" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -11722,45 +11719,45 @@
       <c r="M219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="11" t="inlineStr">
+      <c r="A220" s="8" t="inlineStr">
         <is>
           <t>R0219</t>
         </is>
       </c>
-      <c r="B220" s="11" t="inlineStr">
+      <c r="B220" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C220" s="11" t="inlineStr"/>
-      <c r="D220" s="12" t="n">
+      <c r="C220" s="8" t="inlineStr"/>
+      <c r="D220" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E220" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F220" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G220" s="13" t="n">
+      <c r="E220" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F220" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G220" s="12" t="n">
         <v>-2.774157390045823</v>
       </c>
-      <c r="H220" s="13" t="n">
+      <c r="H220" s="12" t="n">
         <v>0.7883472621162863</v>
       </c>
-      <c r="I220" s="13" t="n">
+      <c r="I220" s="12" t="n">
         <v>0.877766857643871</v>
       </c>
-      <c r="J220" s="13" t="n">
+      <c r="J220" s="12" t="n">
         <v>-0.06650952026751367</v>
       </c>
-      <c r="K220" s="13" t="n">
+      <c r="K220" s="12" t="n">
         <v>0.4048777400508139</v>
       </c>
-      <c r="L220" s="13" t="n">
+      <c r="L220" s="12" t="n">
         <v>-0.1997056371729687</v>
       </c>
-      <c r="M220" s="11" t="inlineStr">
+      <c r="M220" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -11808,135 +11805,135 @@
       <c r="M221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="11" t="inlineStr">
+      <c r="A222" s="8" t="inlineStr">
         <is>
           <t>R0221</t>
         </is>
       </c>
-      <c r="B222" s="11" t="inlineStr">
+      <c r="B222" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C222" s="11" t="inlineStr"/>
-      <c r="D222" s="12" t="n">
+      <c r="C222" s="8" t="inlineStr"/>
+      <c r="D222" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E222" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F222" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G222" s="13" t="n">
+      <c r="E222" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F222" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G222" s="12" t="n">
         <v>0.1113322902113159</v>
       </c>
-      <c r="H222" s="13" t="n">
+      <c r="H222" s="12" t="n">
         <v>0.5439283743054619</v>
       </c>
-      <c r="I222" s="13" t="n">
+      <c r="I222" s="12" t="n">
         <v>1.615064357353946</v>
       </c>
-      <c r="J222" s="13" t="n">
+      <c r="J222" s="12" t="n">
         <v>2.104335935976239</v>
       </c>
-      <c r="K222" s="13" t="n">
+      <c r="K222" s="12" t="n">
         <v>1.881107565423771</v>
       </c>
-      <c r="L222" s="13" t="n">
+      <c r="L222" s="12" t="n">
         <v>2.157705997467955</v>
       </c>
-      <c r="M222" s="11" t="inlineStr">
+      <c r="M222" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="11" t="inlineStr">
+      <c r="A223" s="8" t="inlineStr">
         <is>
           <t>R0222</t>
         </is>
       </c>
-      <c r="B223" s="11" t="inlineStr">
+      <c r="B223" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C223" s="11" t="inlineStr"/>
-      <c r="D223" s="12" t="n">
+      <c r="C223" s="8" t="inlineStr"/>
+      <c r="D223" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="E223" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F223" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G223" s="13" t="n">
+      <c r="E223" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F223" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G223" s="12" t="n">
         <v>0.5444335812258353</v>
       </c>
-      <c r="H223" s="13" t="n">
+      <c r="H223" s="12" t="n">
         <v>0.5338858410554059</v>
       </c>
-      <c r="I223" s="13" t="n">
+      <c r="I223" s="12" t="n">
         <v>1.548252726061209</v>
       </c>
-      <c r="J223" s="13" t="n">
+      <c r="J223" s="12" t="n">
         <v>1.955702512349055</v>
       </c>
-      <c r="K223" s="13" t="n">
+      <c r="K223" s="12" t="n">
         <v>1.691996576988744</v>
       </c>
-      <c r="L223" s="13" t="n">
+      <c r="L223" s="12" t="n">
         <v>1.684498673964232</v>
       </c>
-      <c r="M223" s="11" t="inlineStr">
+      <c r="M223" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="11" t="inlineStr">
+      <c r="A224" s="8" t="inlineStr">
         <is>
           <t>R0223</t>
         </is>
       </c>
-      <c r="B224" s="11" t="inlineStr">
+      <c r="B224" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C224" s="11" t="inlineStr"/>
-      <c r="D224" s="12" t="n">
+      <c r="C224" s="8" t="inlineStr"/>
+      <c r="D224" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E224" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F224" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G224" s="13" t="n">
+      <c r="E224" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F224" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G224" s="12" t="n">
         <v>1.397969313687971</v>
       </c>
-      <c r="H224" s="13" t="n">
+      <c r="H224" s="12" t="n">
         <v>0.5975052009652779</v>
       </c>
-      <c r="I224" s="13" t="n">
+      <c r="I224" s="12" t="n">
         <v>1.021751074320015</v>
       </c>
-      <c r="J224" s="13" t="n">
+      <c r="J224" s="12" t="n">
         <v>0.171259393320293</v>
       </c>
-      <c r="K224" s="13" t="n">
+      <c r="K224" s="12" t="n">
         <v>1.708289917570814</v>
       </c>
-      <c r="L224" s="13" t="n">
+      <c r="L224" s="12" t="n">
         <v>1.170102836012391</v>
       </c>
-      <c r="M224" s="11" t="inlineStr">
+      <c r="M224" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -12353,45 +12350,45 @@
       <c r="M234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="11" t="inlineStr">
+      <c r="A235" s="8" t="inlineStr">
         <is>
           <t>R0234</t>
         </is>
       </c>
-      <c r="B235" s="11" t="inlineStr">
+      <c r="B235" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C235" s="11" t="inlineStr"/>
-      <c r="D235" s="12" t="n">
+      <c r="C235" s="8" t="inlineStr"/>
+      <c r="D235" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="E235" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F235" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G235" s="13" t="n">
+      <c r="E235" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F235" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G235" s="12" t="n">
         <v>-0.5655280740349017</v>
       </c>
-      <c r="H235" s="13" t="n">
+      <c r="H235" s="12" t="n">
         <v>0.5301142963227143</v>
       </c>
-      <c r="I235" s="13" t="n">
+      <c r="I235" s="12" t="n">
         <v>1.365200247117402</v>
       </c>
-      <c r="J235" s="13" t="n">
+      <c r="J235" s="12" t="n">
         <v>1.464780652892</v>
       </c>
-      <c r="K235" s="13" t="n">
+      <c r="K235" s="12" t="n">
         <v>1.501763590906452</v>
       </c>
-      <c r="L235" s="13" t="n">
+      <c r="L235" s="12" t="n">
         <v>1.280609897521813</v>
       </c>
-      <c r="M235" s="11" t="inlineStr">
+      <c r="M235" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -12480,45 +12477,45 @@
       <c r="M237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="11" t="inlineStr">
+      <c r="A238" s="8" t="inlineStr">
         <is>
           <t>R0237</t>
         </is>
       </c>
-      <c r="B238" s="11" t="inlineStr">
+      <c r="B238" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C238" s="11" t="inlineStr"/>
-      <c r="D238" s="12" t="n">
+      <c r="C238" s="8" t="inlineStr"/>
+      <c r="D238" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E238" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F238" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G238" s="13" t="n">
+      <c r="E238" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F238" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G238" s="12" t="n">
         <v>-0.287528625922924</v>
       </c>
-      <c r="H238" s="13" t="n">
+      <c r="H238" s="12" t="n">
         <v>0.525128174663108</v>
       </c>
-      <c r="I238" s="13" t="n">
+      <c r="I238" s="12" t="n">
         <v>0.5366171683780862</v>
       </c>
-      <c r="J238" s="13" t="n">
+      <c r="J238" s="12" t="n">
         <v>-2.307725625496391</v>
       </c>
-      <c r="K238" s="13" t="n">
+      <c r="K238" s="12" t="n">
         <v>0.4479779366527716</v>
       </c>
-      <c r="L238" s="13" t="n">
+      <c r="L238" s="12" t="n">
         <v>-1.956765522854745</v>
       </c>
-      <c r="M238" s="11" t="inlineStr">
+      <c r="M238" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -12607,90 +12604,90 @@
       <c r="M240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="11" t="inlineStr">
+      <c r="A241" s="8" t="inlineStr">
         <is>
           <t>R0240</t>
         </is>
       </c>
-      <c r="B241" s="11" t="inlineStr">
+      <c r="B241" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C241" s="11" t="inlineStr"/>
-      <c r="D241" s="12" t="n">
+      <c r="C241" s="8" t="inlineStr"/>
+      <c r="D241" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E241" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F241" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G241" s="13" t="n">
+      <c r="E241" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F241" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G241" s="12" t="n">
         <v>-1.828758139764982</v>
       </c>
-      <c r="H241" s="13" t="n">
+      <c r="H241" s="12" t="n">
         <v>0.6172109748082045</v>
       </c>
-      <c r="I241" s="13" t="n">
+      <c r="I241" s="12" t="n">
         <v>0.5644436870466313</v>
       </c>
-      <c r="J241" s="13" t="n">
+      <c r="J241" s="12" t="n">
         <v>-1.532977850904929</v>
       </c>
-      <c r="K241" s="13" t="n">
+      <c r="K241" s="12" t="n">
         <v>0.346551397179895</v>
       </c>
-      <c r="L241" s="13" t="n">
+      <c r="L241" s="12" t="n">
         <v>-0.9317285568159822</v>
       </c>
-      <c r="M241" s="11" t="inlineStr">
+      <c r="M241" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="11" t="inlineStr">
+      <c r="A242" s="8" t="inlineStr">
         <is>
           <t>R0241</t>
         </is>
       </c>
-      <c r="B242" s="11" t="inlineStr">
+      <c r="B242" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C242" s="11" t="inlineStr"/>
-      <c r="D242" s="12" t="n">
+      <c r="C242" s="8" t="inlineStr"/>
+      <c r="D242" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="E242" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F242" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G242" s="13" t="n">
+      <c r="E242" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F242" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G242" s="12" t="n">
         <v>-0.7544165989351179</v>
       </c>
-      <c r="H242" s="13" t="n">
+      <c r="H242" s="12" t="n">
         <v>0.5540113276153664</v>
       </c>
-      <c r="I242" s="13" t="n">
+      <c r="I242" s="12" t="n">
         <v>0.6082577777053078</v>
       </c>
-      <c r="J242" s="13" t="n">
+      <c r="J242" s="12" t="n">
         <v>-1.73499403389</v>
       </c>
-      <c r="K242" s="13" t="n">
+      <c r="K242" s="12" t="n">
         <v>0.4749834654157061</v>
       </c>
-      <c r="L242" s="13" t="n">
+      <c r="L242" s="12" t="n">
         <v>-1.377139730685456</v>
       </c>
-      <c r="M242" s="11" t="inlineStr">
+      <c r="M242" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -12902,45 +12899,45 @@
       <c r="M247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="11" t="inlineStr">
+      <c r="A248" s="8" t="inlineStr">
         <is>
           <t>R0247</t>
         </is>
       </c>
-      <c r="B248" s="11" t="inlineStr">
+      <c r="B248" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C248" s="11" t="inlineStr"/>
-      <c r="D248" s="12" t="n">
+      <c r="C248" s="8" t="inlineStr"/>
+      <c r="D248" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="E248" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F248" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G248" s="13" t="n">
+      <c r="E248" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F248" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G248" s="12" t="n">
         <v>0.5444335812258353</v>
       </c>
-      <c r="H248" s="13" t="n">
+      <c r="H248" s="12" t="n">
         <v>0.5338858410554059</v>
       </c>
-      <c r="I248" s="13" t="n">
+      <c r="I248" s="12" t="n">
         <v>1.348306565930796</v>
       </c>
-      <c r="J248" s="13" t="n">
+      <c r="J248" s="12" t="n">
         <v>1.33381193370576</v>
       </c>
-      <c r="K248" s="13" t="n">
+      <c r="K248" s="12" t="n">
         <v>1.638700082497109</v>
       </c>
-      <c r="L248" s="13" t="n">
+      <c r="L248" s="12" t="n">
         <v>1.581425464146849</v>
       </c>
-      <c r="M248" s="11" t="inlineStr">
+      <c r="M248" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -13070,45 +13067,45 @@
       <c r="M251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="11" t="inlineStr">
+      <c r="A252" s="8" t="inlineStr">
         <is>
           <t>R0251</t>
         </is>
       </c>
-      <c r="B252" s="11" t="inlineStr">
+      <c r="B252" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C252" s="11" t="inlineStr"/>
-      <c r="D252" s="12" t="n">
+      <c r="C252" s="8" t="inlineStr"/>
+      <c r="D252" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E252" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F252" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G252" s="13" t="n">
+      <c r="E252" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F252" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G252" s="12" t="n">
         <v>-1.47206402952562</v>
       </c>
-      <c r="H252" s="13" t="n">
+      <c r="H252" s="12" t="n">
         <v>0.5798549876787141</v>
       </c>
-      <c r="I252" s="13" t="n">
+      <c r="I252" s="12" t="n">
         <v>1.155144358805684</v>
       </c>
-      <c r="J252" s="13" t="n">
+      <c r="J252" s="12" t="n">
         <v>0.6246125181863492</v>
       </c>
-      <c r="K252" s="13" t="n">
+      <c r="K252" s="12" t="n">
         <v>1.625143176453557</v>
       </c>
-      <c r="L252" s="13" t="n">
+      <c r="L252" s="12" t="n">
         <v>1.060252988700532</v>
       </c>
-      <c r="M252" s="11" t="inlineStr">
+      <c r="M252" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -13156,45 +13153,45 @@
       <c r="M253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="11" t="inlineStr">
+      <c r="A254" s="8" t="inlineStr">
         <is>
           <t>R0253</t>
         </is>
       </c>
-      <c r="B254" s="11" t="inlineStr">
+      <c r="B254" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C254" s="11" t="inlineStr"/>
-      <c r="D254" s="12" t="n">
+      <c r="C254" s="8" t="inlineStr"/>
+      <c r="D254" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="E254" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F254" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G254" s="13" t="n">
+      <c r="E254" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F254" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G254" s="12" t="n">
         <v>1.129435189615007</v>
       </c>
-      <c r="H254" s="13" t="n">
+      <c r="H254" s="12" t="n">
         <v>0.5642541619317639</v>
       </c>
-      <c r="I254" s="13" t="n">
+      <c r="I254" s="12" t="n">
         <v>1.163527026480374</v>
       </c>
-      <c r="J254" s="13" t="n">
+      <c r="J254" s="12" t="n">
         <v>0.6653501821865404</v>
       </c>
-      <c r="K254" s="13" t="n">
+      <c r="K254" s="12" t="n">
         <v>1.642142185977306</v>
       </c>
-      <c r="L254" s="13" t="n">
+      <c r="L254" s="12" t="n">
         <v>1.340892894137387</v>
       </c>
-      <c r="M254" s="11" t="inlineStr">
+      <c r="M254" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -13447,45 +13444,45 @@
       <c r="M260" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="11" t="inlineStr">
+      <c r="A261" s="8" t="inlineStr">
         <is>
           <t>R0260</t>
         </is>
       </c>
-      <c r="B261" s="11" t="inlineStr">
+      <c r="B261" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C261" s="11" t="inlineStr"/>
-      <c r="D261" s="12" t="n">
+      <c r="C261" s="8" t="inlineStr"/>
+      <c r="D261" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="E261" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F261" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G261" s="13" t="n">
+      <c r="E261" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F261" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G261" s="12" t="n">
         <v>0.8093892308583343</v>
       </c>
-      <c r="H261" s="13" t="n">
+      <c r="H261" s="12" t="n">
         <v>0.5503992143612544</v>
       </c>
-      <c r="I261" s="13" t="n">
+      <c r="I261" s="12" t="n">
         <v>1.63649719430896</v>
       </c>
-      <c r="J261" s="13" t="n">
+      <c r="J261" s="12" t="n">
         <v>2.170359125674516</v>
       </c>
-      <c r="K261" s="13" t="n">
+      <c r="K261" s="12" t="n">
         <v>1.567190835820263</v>
       </c>
-      <c r="L261" s="13" t="n">
+      <c r="L261" s="12" t="n">
         <v>1.315599507865624</v>
       </c>
-      <c r="M261" s="11" t="inlineStr">
+      <c r="M261" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -13820,45 +13817,45 @@
       <c r="M269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="11" t="inlineStr">
+      <c r="A270" s="8" t="inlineStr">
         <is>
           <t>R0269</t>
         </is>
       </c>
-      <c r="B270" s="11" t="inlineStr">
+      <c r="B270" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C270" s="11" t="inlineStr"/>
-      <c r="D270" s="12" t="n">
+      <c r="C270" s="8" t="inlineStr"/>
+      <c r="D270" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="E270" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F270" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G270" s="13" t="n">
+      <c r="E270" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F270" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G270" s="12" t="n">
         <v>2.795636414735082</v>
       </c>
-      <c r="H270" s="13" t="n">
+      <c r="H270" s="12" t="n">
         <v>0.7930629618978372</v>
       </c>
-      <c r="I270" s="13" t="n">
+      <c r="I270" s="12" t="n">
         <v>0.9796101693485277</v>
       </c>
-      <c r="J270" s="13" t="n">
+      <c r="J270" s="12" t="n">
         <v>0.1338392223072377</v>
       </c>
-      <c r="K270" s="13" t="n">
+      <c r="K270" s="12" t="n">
         <v>0.4801205831778185</v>
       </c>
-      <c r="L270" s="13" t="n">
+      <c r="L270" s="12" t="n">
         <v>-0.1032821645937466</v>
       </c>
-      <c r="M270" s="11" t="inlineStr">
+      <c r="M270" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -13988,45 +13985,45 @@
       <c r="M273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="11" t="inlineStr">
+      <c r="A274" s="8" t="inlineStr">
         <is>
           <t>R0273</t>
         </is>
       </c>
-      <c r="B274" s="11" t="inlineStr">
+      <c r="B274" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C274" s="11" t="inlineStr"/>
-      <c r="D274" s="12" t="n">
+      <c r="C274" s="8" t="inlineStr"/>
+      <c r="D274" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="E274" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F274" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G274" s="13" t="n">
+      <c r="E274" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F274" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G274" s="12" t="n">
         <v>1.055404856435562</v>
       </c>
-      <c r="H274" s="13" t="n">
+      <c r="H274" s="12" t="n">
         <v>0.574590098781474</v>
       </c>
-      <c r="I274" s="13" t="n">
+      <c r="I274" s="12" t="n">
         <v>1.517065051446698</v>
       </c>
-      <c r="J274" s="13" t="n">
+      <c r="J274" s="12" t="n">
         <v>1.69477779536513</v>
       </c>
-      <c r="K274" s="13" t="n">
+      <c r="K274" s="12" t="n">
         <v>1.483482869933285</v>
       </c>
-      <c r="L274" s="13" t="n">
+      <c r="L274" s="12" t="n">
         <v>1.010637069504324</v>
       </c>
-      <c r="M274" s="11" t="inlineStr">
+      <c r="M274" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -14279,45 +14276,45 @@
       <c r="M280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="11" t="inlineStr">
+      <c r="A281" s="8" t="inlineStr">
         <is>
           <t>R0280</t>
         </is>
       </c>
-      <c r="B281" s="11" t="inlineStr">
+      <c r="B281" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C281" s="11" t="inlineStr"/>
-      <c r="D281" s="12" t="n">
+      <c r="C281" s="8" t="inlineStr"/>
+      <c r="D281" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="E281" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F281" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G281" s="13" t="n">
+      <c r="E281" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F281" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G281" s="12" t="n">
         <v>1.122420806974637</v>
       </c>
-      <c r="H281" s="13" t="n">
+      <c r="H281" s="12" t="n">
         <v>0.5656219018187126</v>
       </c>
-      <c r="I281" s="13" t="n">
+      <c r="I281" s="12" t="n">
         <v>1.303753436824619</v>
       </c>
-      <c r="J281" s="13" t="n">
+      <c r="J281" s="12" t="n">
         <v>1.120683180010422</v>
       </c>
-      <c r="K281" s="13" t="n">
+      <c r="K281" s="12" t="n">
         <v>1.733191190794106</v>
       </c>
-      <c r="L281" s="13" t="n">
+      <c r="L281" s="12" t="n">
         <v>1.412369130495166</v>
       </c>
-      <c r="M281" s="11" t="inlineStr">
+      <c r="M281" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -14447,45 +14444,45 @@
       <c r="M284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="11" t="inlineStr">
+      <c r="A285" s="8" t="inlineStr">
         <is>
           <t>R0284</t>
         </is>
       </c>
-      <c r="B285" s="11" t="inlineStr">
+      <c r="B285" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C285" s="11" t="inlineStr"/>
-      <c r="D285" s="12" t="n">
+      <c r="C285" s="8" t="inlineStr"/>
+      <c r="D285" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E285" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F285" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G285" s="13" t="n">
+      <c r="E285" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F285" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G285" s="12" t="n">
         <v>1.383069699843956</v>
       </c>
-      <c r="H285" s="13" t="n">
+      <c r="H285" s="12" t="n">
         <v>0.5987161505018075</v>
       </c>
-      <c r="I285" s="13" t="n">
+      <c r="I285" s="12" t="n">
         <v>0.659957053011016</v>
       </c>
-      <c r="J285" s="13" t="n">
+      <c r="J285" s="12" t="n">
         <v>-1.215688082256401</v>
       </c>
-      <c r="K285" s="13" t="n">
+      <c r="K285" s="12" t="n">
         <v>0.4727482362272081</v>
       </c>
-      <c r="L285" s="13" t="n">
+      <c r="L285" s="12" t="n">
         <v>-0.9006564700935317</v>
       </c>
-      <c r="M285" s="11" t="inlineStr">
+      <c r="M285" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -14943,45 +14940,45 @@
       <c r="M296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="11" t="inlineStr">
+      <c r="A297" s="8" t="inlineStr">
         <is>
           <t>R0296</t>
         </is>
       </c>
-      <c r="B297" s="11" t="inlineStr">
+      <c r="B297" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C297" s="11" t="inlineStr"/>
-      <c r="D297" s="12" t="n">
+      <c r="C297" s="8" t="inlineStr"/>
+      <c r="D297" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E297" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F297" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G297" s="13" t="n">
+      <c r="E297" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F297" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G297" s="12" t="n">
         <v>1.83438499511204</v>
       </c>
-      <c r="H297" s="13" t="n">
+      <c r="H297" s="12" t="n">
         <v>0.6237713435108156</v>
       </c>
-      <c r="I297" s="13" t="n">
+      <c r="I297" s="12" t="n">
         <v>0.7444768797343259</v>
       </c>
-      <c r="J297" s="13" t="n">
+      <c r="J297" s="12" t="n">
         <v>-0.7604541322798504</v>
       </c>
-      <c r="K297" s="13" t="n">
+      <c r="K297" s="12" t="n">
         <v>0.4417543087034158</v>
       </c>
-      <c r="L297" s="13" t="n">
+      <c r="L297" s="12" t="n">
         <v>-0.716034265953326</v>
       </c>
-      <c r="M297" s="11" t="inlineStr">
+      <c r="M297" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -15070,45 +15067,45 @@
       <c r="M299" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="11" t="inlineStr">
+      <c r="A300" s="8" t="inlineStr">
         <is>
           <t>R0299</t>
         </is>
       </c>
-      <c r="B300" s="11" t="inlineStr">
+      <c r="B300" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C300" s="11" t="inlineStr"/>
-      <c r="D300" s="12" t="n">
+      <c r="C300" s="8" t="inlineStr"/>
+      <c r="D300" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E300" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F300" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G300" s="13" t="n">
+      <c r="E300" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F300" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G300" s="12" t="n">
         <v>2.258651488166693</v>
       </c>
-      <c r="H300" s="13" t="n">
+      <c r="H300" s="12" t="n">
         <v>0.6836617924804415</v>
       </c>
-      <c r="I300" s="13" t="n">
+      <c r="I300" s="12" t="n">
         <v>0.7804748924361813</v>
       </c>
-      <c r="J300" s="13" t="n">
+      <c r="J300" s="12" t="n">
         <v>-0.4845232340183716</v>
       </c>
-      <c r="K300" s="13" t="n">
+      <c r="K300" s="12" t="n">
         <v>0.418549798156424</v>
       </c>
-      <c r="L300" s="13" t="n">
+      <c r="L300" s="12" t="n">
         <v>-0.4928490851100056</v>
       </c>
-      <c r="M300" s="11" t="inlineStr">
+      <c r="M300" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -15238,45 +15235,45 @@
       <c r="M303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="11" t="inlineStr">
+      <c r="A304" s="8" t="inlineStr">
         <is>
           <t>R0303</t>
         </is>
       </c>
-      <c r="B304" s="11" t="inlineStr">
+      <c r="B304" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C304" s="11" t="inlineStr"/>
-      <c r="D304" s="12" t="n">
+      <c r="C304" s="8" t="inlineStr"/>
+      <c r="D304" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="E304" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F304" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G304" s="13" t="n">
+      <c r="E304" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F304" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G304" s="12" t="n">
         <v>1.031016934019928</v>
       </c>
-      <c r="H304" s="13" t="n">
+      <c r="H304" s="12" t="n">
         <v>0.5758368748724687</v>
       </c>
-      <c r="I304" s="13" t="n">
+      <c r="I304" s="12" t="n">
         <v>1.556585025434358</v>
       </c>
-      <c r="J304" s="13" t="n">
+      <c r="J304" s="12" t="n">
         <v>1.768926526968115</v>
       </c>
-      <c r="K304" s="13" t="n">
+      <c r="K304" s="12" t="n">
         <v>1.715853188600704</v>
       </c>
-      <c r="L304" s="13" t="n">
+      <c r="L304" s="12" t="n">
         <v>1.361547757315634</v>
       </c>
-      <c r="M304" s="11" t="inlineStr">
+      <c r="M304" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -15447,45 +15444,45 @@
       <c r="M308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="11" t="inlineStr">
+      <c r="A309" s="8" t="inlineStr">
         <is>
           <t>R0308</t>
         </is>
       </c>
-      <c r="B309" s="11" t="inlineStr">
+      <c r="B309" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C309" s="11" t="inlineStr"/>
-      <c r="D309" s="12" t="n">
+      <c r="C309" s="8" t="inlineStr"/>
+      <c r="D309" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="E309" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F309" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G309" s="13" t="n">
+      <c r="E309" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F309" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G309" s="12" t="n">
         <v>-0.3516725190438215</v>
       </c>
-      <c r="H309" s="13" t="n">
+      <c r="H309" s="12" t="n">
         <v>0.539375549402296</v>
       </c>
-      <c r="I309" s="13" t="n">
+      <c r="I309" s="12" t="n">
         <v>1.48103480421567</v>
       </c>
-      <c r="J309" s="13" t="n">
+      <c r="J309" s="12" t="n">
         <v>1.836815970179392</v>
       </c>
-      <c r="K309" s="13" t="n">
+      <c r="K309" s="12" t="n">
         <v>1.699340922285331</v>
       </c>
-      <c r="L309" s="13" t="n">
+      <c r="L309" s="12" t="n">
         <v>1.735094424155153</v>
       </c>
-      <c r="M309" s="11" t="inlineStr">
+      <c r="M309" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -15656,45 +15653,45 @@
       <c r="M313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="11" t="inlineStr">
+      <c r="A314" s="8" t="inlineStr">
         <is>
           <t>R0313</t>
         </is>
       </c>
-      <c r="B314" s="11" t="inlineStr">
+      <c r="B314" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C314" s="11" t="inlineStr"/>
-      <c r="D314" s="12" t="n">
+      <c r="C314" s="8" t="inlineStr"/>
+      <c r="D314" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E314" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F314" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G314" s="13" t="n">
+      <c r="E314" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F314" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G314" s="12" t="n">
         <v>1.46967040698167</v>
       </c>
-      <c r="H314" s="13" t="n">
+      <c r="H314" s="12" t="n">
         <v>0.5865582715673844</v>
       </c>
-      <c r="I314" s="13" t="n">
+      <c r="I314" s="12" t="n">
         <v>0.5103212431883087</v>
       </c>
-      <c r="J314" s="13" t="n">
+      <c r="J314" s="12" t="n">
         <v>-1.972621252969997</v>
       </c>
-      <c r="K314" s="13" t="n">
+      <c r="K314" s="12" t="n">
         <v>0.3486480899333768</v>
       </c>
-      <c r="L314" s="13" t="n">
+      <c r="L314" s="12" t="n">
         <v>-1.270329482963547</v>
       </c>
-      <c r="M314" s="11" t="inlineStr">
+      <c r="M314" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -16029,45 +16026,45 @@
       <c r="M322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="11" t="inlineStr">
+      <c r="A323" s="8" t="inlineStr">
         <is>
           <t>R0322</t>
         </is>
       </c>
-      <c r="B323" s="11" t="inlineStr">
+      <c r="B323" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C323" s="11" t="inlineStr"/>
-      <c r="D323" s="12" t="n">
+      <c r="C323" s="8" t="inlineStr"/>
+      <c r="D323" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E323" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F323" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G323" s="13" t="n">
+      <c r="E323" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F323" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G323" s="12" t="n">
         <v>2.258651488166693</v>
       </c>
-      <c r="H323" s="13" t="n">
+      <c r="H323" s="12" t="n">
         <v>0.6836617924804415</v>
       </c>
-      <c r="I323" s="13" t="n">
+      <c r="I323" s="12" t="n">
         <v>0.7349689277077399</v>
       </c>
-      <c r="J323" s="13" t="n">
+      <c r="J323" s="12" t="n">
         <v>-0.6257987167500069</v>
       </c>
-      <c r="K323" s="13" t="n">
+      <c r="K323" s="12" t="n">
         <v>0.3953013825970998</v>
       </c>
-      <c r="L323" s="13" t="n">
+      <c r="L323" s="12" t="n">
         <v>-0.5379757516436521</v>
       </c>
-      <c r="M323" s="11" t="inlineStr">
+      <c r="M323" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -16115,45 +16112,45 @@
       <c r="M324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" s="11" t="inlineStr">
+      <c r="A325" s="8" t="inlineStr">
         <is>
           <t>R0324</t>
         </is>
       </c>
-      <c r="B325" s="11" t="inlineStr">
+      <c r="B325" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C325" s="11" t="inlineStr"/>
-      <c r="D325" s="12" t="n">
+      <c r="C325" s="8" t="inlineStr"/>
+      <c r="D325" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E325" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F325" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G325" s="13" t="n">
+      <c r="E325" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F325" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G325" s="12" t="n">
         <v>1.140817678674626</v>
       </c>
-      <c r="H325" s="13" t="n">
+      <c r="H325" s="12" t="n">
         <v>0.5618791360218677</v>
       </c>
-      <c r="I325" s="13" t="n">
+      <c r="I325" s="12" t="n">
         <v>1.433735478995187</v>
       </c>
-      <c r="J325" s="13" t="n">
+      <c r="J325" s="12" t="n">
         <v>1.49296786119645</v>
       </c>
-      <c r="K325" s="13" t="n">
+      <c r="K325" s="12" t="n">
         <v>2.214939214404491</v>
       </c>
-      <c r="L325" s="13" t="n">
+      <c r="L325" s="12" t="n">
         <v>1.986108916861249</v>
       </c>
-      <c r="M325" s="11" t="inlineStr">
+      <c r="M325" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -16529,45 +16526,45 @@
       <c r="M334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" s="11" t="inlineStr">
+      <c r="A335" s="8" t="inlineStr">
         <is>
           <t>R0334</t>
         </is>
       </c>
-      <c r="B335" s="11" t="inlineStr">
+      <c r="B335" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C335" s="11" t="inlineStr"/>
-      <c r="D335" s="12" t="n">
+      <c r="C335" s="8" t="inlineStr"/>
+      <c r="D335" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E335" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F335" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G335" s="13" t="n">
+      <c r="E335" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F335" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G335" s="12" t="n">
         <v>2.258651488166693</v>
       </c>
-      <c r="H335" s="13" t="n">
+      <c r="H335" s="12" t="n">
         <v>0.6836617924804415</v>
       </c>
-      <c r="I335" s="13" t="n">
+      <c r="I335" s="12" t="n">
         <v>0.8577352961646858</v>
       </c>
-      <c r="J335" s="13" t="n">
+      <c r="J335" s="12" t="n">
         <v>-0.2567468182741041</v>
       </c>
-      <c r="K335" s="13" t="n">
+      <c r="K335" s="12" t="n">
         <v>0.4530475513762882</v>
       </c>
-      <c r="L335" s="13" t="n">
+      <c r="L335" s="12" t="n">
         <v>-0.4288691409241072</v>
       </c>
-      <c r="M335" s="11" t="inlineStr">
+      <c r="M335" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -16656,45 +16653,45 @@
       <c r="M337" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" s="11" t="inlineStr">
+      <c r="A338" s="8" t="inlineStr">
         <is>
           <t>R0337</t>
         </is>
       </c>
-      <c r="B338" s="11" t="inlineStr">
+      <c r="B338" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C338" s="11" t="inlineStr"/>
-      <c r="D338" s="12" t="n">
+      <c r="C338" s="8" t="inlineStr"/>
+      <c r="D338" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E338" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F338" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G338" s="13" t="n">
+      <c r="E338" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F338" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G338" s="12" t="n">
         <v>-0.287528625922924</v>
       </c>
-      <c r="H338" s="13" t="n">
+      <c r="H338" s="12" t="n">
         <v>0.525128174663108</v>
       </c>
-      <c r="I338" s="13" t="n">
+      <c r="I338" s="12" t="n">
         <v>1.129105085465356</v>
       </c>
-      <c r="J338" s="13" t="n">
+      <c r="J338" s="12" t="n">
         <v>0.6045446460729689</v>
       </c>
-      <c r="K338" s="13" t="n">
+      <c r="K338" s="12" t="n">
         <v>1.589873897225996</v>
       </c>
-      <c r="L338" s="13" t="n">
+      <c r="L338" s="12" t="n">
         <v>1.586791290384482</v>
       </c>
-      <c r="M338" s="11" t="inlineStr">
+      <c r="M338" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -16742,45 +16739,45 @@
       <c r="M339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="11" t="inlineStr">
+      <c r="A340" s="8" t="inlineStr">
         <is>
           <t>R0339</t>
         </is>
       </c>
-      <c r="B340" s="11" t="inlineStr">
+      <c r="B340" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C340" s="11" t="inlineStr"/>
-      <c r="D340" s="12" t="n">
+      <c r="C340" s="8" t="inlineStr"/>
+      <c r="D340" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E340" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F340" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G340" s="13" t="n">
+      <c r="E340" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F340" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G340" s="12" t="n">
         <v>-1.379252800186247</v>
       </c>
-      <c r="H340" s="13" t="n">
+      <c r="H340" s="12" t="n">
         <v>0.5918605280400128</v>
       </c>
-      <c r="I340" s="13" t="n">
+      <c r="I340" s="12" t="n">
         <v>1.344831246095107</v>
       </c>
-      <c r="J340" s="13" t="n">
+      <c r="J340" s="12" t="n">
         <v>1.203083393952848</v>
       </c>
-      <c r="K340" s="13" t="n">
+      <c r="K340" s="12" t="n">
         <v>1.570048632958382</v>
       </c>
-      <c r="L340" s="13" t="n">
+      <c r="L340" s="12" t="n">
         <v>0.9979497723381284</v>
       </c>
-      <c r="M340" s="11" t="inlineStr">
+      <c r="M340" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -16828,90 +16825,90 @@
       <c r="M341" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" s="11" t="inlineStr">
+      <c r="A342" s="8" t="inlineStr">
         <is>
           <t>R0341</t>
         </is>
       </c>
-      <c r="B342" s="11" t="inlineStr">
+      <c r="B342" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C342" s="11" t="inlineStr"/>
-      <c r="D342" s="12" t="n">
+      <c r="C342" s="8" t="inlineStr"/>
+      <c r="D342" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E342" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F342" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G342" s="13" t="n">
+      <c r="E342" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F342" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G342" s="12" t="n">
         <v>1.83438499511204</v>
       </c>
-      <c r="H342" s="13" t="n">
+      <c r="H342" s="12" t="n">
         <v>0.6237713435108156</v>
       </c>
-      <c r="I342" s="13" t="n">
+      <c r="I342" s="12" t="n">
         <v>1.447988076095944</v>
       </c>
-      <c r="J342" s="13" t="n">
+      <c r="J342" s="12" t="n">
         <v>1.325232074981375</v>
       </c>
-      <c r="K342" s="13" t="n">
+      <c r="K342" s="12" t="n">
         <v>3.020476155431308</v>
       </c>
-      <c r="L342" s="13" t="n">
+      <c r="L342" s="12" t="n">
         <v>2.047981889110922</v>
       </c>
-      <c r="M342" s="11" t="inlineStr">
+      <c r="M342" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="11" t="inlineStr">
+      <c r="A343" s="8" t="inlineStr">
         <is>
           <t>R0342</t>
         </is>
       </c>
-      <c r="B343" s="11" t="inlineStr">
+      <c r="B343" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C343" s="11" t="inlineStr"/>
-      <c r="D343" s="12" t="n">
+      <c r="C343" s="8" t="inlineStr"/>
+      <c r="D343" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E343" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F343" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G343" s="13" t="n">
+      <c r="E343" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F343" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G343" s="12" t="n">
         <v>1.140817678674626</v>
       </c>
-      <c r="H343" s="13" t="n">
+      <c r="H343" s="12" t="n">
         <v>0.5618791360218677</v>
       </c>
-      <c r="I343" s="13" t="n">
+      <c r="I343" s="12" t="n">
         <v>1.068965259220369</v>
       </c>
-      <c r="J343" s="13" t="n">
+      <c r="J343" s="12" t="n">
         <v>0.3379937332955212</v>
       </c>
-      <c r="K343" s="13" t="n">
+      <c r="K343" s="12" t="n">
         <v>1.519440853754869</v>
       </c>
-      <c r="L343" s="13" t="n">
+      <c r="L343" s="12" t="n">
         <v>1.063732689030426</v>
       </c>
-      <c r="M343" s="11" t="inlineStr">
+      <c r="M343" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -17205,45 +17202,45 @@
       <c r="M350" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" s="11" t="inlineStr">
+      <c r="A351" s="8" t="inlineStr">
         <is>
           <t>R0350</t>
         </is>
       </c>
-      <c r="B351" s="11" t="inlineStr">
+      <c r="B351" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C351" s="11" t="inlineStr"/>
-      <c r="D351" s="12" t="n">
+      <c r="C351" s="8" t="inlineStr"/>
+      <c r="D351" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="E351" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F351" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G351" s="13" t="n">
+      <c r="E351" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F351" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G351" s="12" t="n">
         <v>-0.5655280740349017</v>
       </c>
-      <c r="H351" s="13" t="n">
+      <c r="H351" s="12" t="n">
         <v>0.5301142963227143</v>
       </c>
-      <c r="I351" s="13" t="n">
+      <c r="I351" s="12" t="n">
         <v>1.62468966978547</v>
       </c>
-      <c r="J351" s="13" t="n">
+      <c r="J351" s="12" t="n">
         <v>2.30449004814884</v>
       </c>
-      <c r="K351" s="13" t="n">
+      <c r="K351" s="12" t="n">
         <v>1.889926044353263</v>
       </c>
-      <c r="L351" s="13" t="n">
+      <c r="L351" s="12" t="n">
         <v>2.006253959281489</v>
       </c>
-      <c r="M351" s="11" t="inlineStr">
+      <c r="M351" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -17373,45 +17370,45 @@
       <c r="M354" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="11" t="inlineStr">
+      <c r="A355" s="8" t="inlineStr">
         <is>
           <t>R0354</t>
         </is>
       </c>
-      <c r="B355" s="11" t="inlineStr">
+      <c r="B355" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C355" s="11" t="inlineStr"/>
-      <c r="D355" s="12" t="n">
+      <c r="C355" s="8" t="inlineStr"/>
+      <c r="D355" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E355" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F355" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G355" s="13" t="n">
+      <c r="E355" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F355" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G355" s="12" t="n">
         <v>-1.150656487421848</v>
       </c>
-      <c r="H355" s="13" t="n">
+      <c r="H355" s="12" t="n">
         <v>0.5556231849011074</v>
       </c>
-      <c r="I355" s="13" t="n">
+      <c r="I355" s="12" t="n">
         <v>1.356267247210101</v>
       </c>
-      <c r="J355" s="13" t="n">
+      <c r="J355" s="12" t="n">
         <v>1.342734117503379</v>
       </c>
-      <c r="K355" s="13" t="n">
+      <c r="K355" s="12" t="n">
         <v>2.332658599008539</v>
       </c>
-      <c r="L355" s="13" t="n">
+      <c r="L355" s="12" t="n">
         <v>2.077585816838184</v>
       </c>
-      <c r="M355" s="11" t="inlineStr">
+      <c r="M355" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -17623,45 +17620,45 @@
       <c r="M360" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" s="11" t="inlineStr">
+      <c r="A361" s="8" t="inlineStr">
         <is>
           <t>R0360</t>
         </is>
       </c>
-      <c r="B361" s="11" t="inlineStr">
+      <c r="B361" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C361" s="11" t="inlineStr"/>
-      <c r="D361" s="12" t="n">
+      <c r="C361" s="8" t="inlineStr"/>
+      <c r="D361" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E361" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F361" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G361" s="13" t="n">
+      <c r="E361" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F361" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G361" s="12" t="n">
         <v>1.140817678674626</v>
       </c>
-      <c r="H361" s="13" t="n">
+      <c r="H361" s="12" t="n">
         <v>0.5618791360218677</v>
       </c>
-      <c r="I361" s="13" t="n">
+      <c r="I361" s="12" t="n">
         <v>0.5864874799042892</v>
       </c>
-      <c r="J361" s="13" t="n">
+      <c r="J361" s="12" t="n">
         <v>-1.699245008705878</v>
       </c>
-      <c r="K361" s="13" t="n">
+      <c r="K361" s="12" t="n">
         <v>0.4388308468310444</v>
       </c>
-      <c r="L361" s="13" t="n">
+      <c r="L361" s="12" t="n">
         <v>-1.272155067925329</v>
       </c>
-      <c r="M361" s="11" t="inlineStr">
+      <c r="M361" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -17914,45 +17911,45 @@
       <c r="M367" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" s="11" t="inlineStr">
+      <c r="A368" s="8" t="inlineStr">
         <is>
           <t>R0367</t>
         </is>
       </c>
-      <c r="B368" s="11" t="inlineStr">
+      <c r="B368" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C368" s="11" t="inlineStr"/>
-      <c r="D368" s="12" t="n">
+      <c r="C368" s="8" t="inlineStr"/>
+      <c r="D368" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E368" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F368" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G368" s="13" t="n">
+      <c r="E368" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F368" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G368" s="12" t="n">
         <v>-3.581882758679049</v>
       </c>
-      <c r="H368" s="13" t="n">
+      <c r="H368" s="12" t="n">
         <v>1.057444586258655</v>
       </c>
-      <c r="I368" s="13" t="n">
+      <c r="I368" s="12" t="n">
         <v>1.19141605680724</v>
       </c>
-      <c r="J368" s="13" t="n">
+      <c r="J368" s="12" t="n">
         <v>0.4955846134836338</v>
       </c>
-      <c r="K368" s="13" t="n">
+      <c r="K368" s="12" t="n">
         <v>2.619466276355285</v>
       </c>
-      <c r="L368" s="13" t="n">
+      <c r="L368" s="12" t="n">
         <v>1.23043990848208</v>
       </c>
-      <c r="M368" s="11" t="inlineStr">
+      <c r="M368" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -18000,45 +17997,45 @@
       <c r="M369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" s="11" t="inlineStr">
+      <c r="A370" s="8" t="inlineStr">
         <is>
           <t>R0369</t>
         </is>
       </c>
-      <c r="B370" s="11" t="inlineStr">
+      <c r="B370" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C370" s="11" t="inlineStr"/>
-      <c r="D370" s="12" t="n">
+      <c r="C370" s="8" t="inlineStr"/>
+      <c r="D370" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E370" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F370" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G370" s="13" t="n">
+      <c r="E370" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F370" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G370" s="12" t="n">
         <v>-1.367921188252948</v>
       </c>
-      <c r="H370" s="13" t="n">
+      <c r="H370" s="12" t="n">
         <v>0.5923103688929841</v>
       </c>
-      <c r="I370" s="13" t="n">
+      <c r="I370" s="12" t="n">
         <v>1.178485717926383</v>
       </c>
-      <c r="J370" s="13" t="n">
+      <c r="J370" s="12" t="n">
         <v>0.690628843402001</v>
       </c>
-      <c r="K370" s="13" t="n">
+      <c r="K370" s="12" t="n">
         <v>1.81526543973753</v>
       </c>
-      <c r="L370" s="13" t="n">
+      <c r="L370" s="12" t="n">
         <v>1.284287620177602</v>
       </c>
-      <c r="M370" s="11" t="inlineStr">
+      <c r="M370" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -18209,90 +18206,90 @@
       <c r="M374" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="11" t="inlineStr">
+      <c r="A375" s="8" t="inlineStr">
         <is>
           <t>R0374</t>
         </is>
       </c>
-      <c r="B375" s="11" t="inlineStr">
+      <c r="B375" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C375" s="11" t="inlineStr"/>
-      <c r="D375" s="12" t="n">
+      <c r="C375" s="8" t="inlineStr"/>
+      <c r="D375" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E375" s="11" t="n">
+      <c r="E375" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F375" s="11" t="n">
+      <c r="F375" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="G375" s="13" t="n">
+      <c r="G375" s="12" t="n">
         <v>-3.478816333716012</v>
       </c>
-      <c r="H375" s="13" t="n">
+      <c r="H375" s="12" t="n">
         <v>1.065686003477773</v>
       </c>
-      <c r="I375" s="13" t="n">
+      <c r="I375" s="12" t="n">
         <v>0.7939041237297038</v>
       </c>
-      <c r="J375" s="13" t="n">
+      <c r="J375" s="12" t="n">
         <v>0.01052728286277299</v>
       </c>
-      <c r="K375" s="13" t="n">
+      <c r="K375" s="12" t="n">
         <v>0.2573399045803349</v>
       </c>
-      <c r="L375" s="13" t="n">
+      <c r="L375" s="12" t="n">
         <v>0.1083464893562801</v>
       </c>
-      <c r="M375" s="11" t="inlineStr">
+      <c r="M375" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="11" t="inlineStr">
+      <c r="A376" s="8" t="inlineStr">
         <is>
           <t>R0375</t>
         </is>
       </c>
-      <c r="B376" s="11" t="inlineStr">
+      <c r="B376" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C376" s="11" t="inlineStr"/>
-      <c r="D376" s="12" t="n">
+      <c r="C376" s="8" t="inlineStr"/>
+      <c r="D376" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E376" s="11" t="n">
+      <c r="E376" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F376" s="11" t="n">
+      <c r="F376" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="G376" s="13" t="n">
+      <c r="G376" s="12" t="n">
         <v>0.2123370097328682</v>
       </c>
-      <c r="H376" s="13" t="n">
+      <c r="H376" s="12" t="n">
         <v>0.554644387631216</v>
       </c>
-      <c r="I376" s="13" t="n">
+      <c r="I376" s="12" t="n">
         <v>1.181486278655191</v>
       </c>
-      <c r="J376" s="13" t="n">
+      <c r="J376" s="12" t="n">
         <v>0.7596245323397435</v>
       </c>
-      <c r="K376" s="13" t="n">
+      <c r="K376" s="12" t="n">
         <v>1.575522613950145</v>
       </c>
-      <c r="L376" s="13" t="n">
+      <c r="L376" s="12" t="n">
         <v>1.511639961082045</v>
       </c>
-      <c r="M376" s="11" t="inlineStr">
+      <c r="M376" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -18340,45 +18337,45 @@
       <c r="M377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" s="11" t="inlineStr">
+      <c r="A378" s="8" t="inlineStr">
         <is>
           <t>R0377</t>
         </is>
       </c>
-      <c r="B378" s="11" t="inlineStr">
+      <c r="B378" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C378" s="11" t="inlineStr"/>
-      <c r="D378" s="12" t="n">
+      <c r="C378" s="8" t="inlineStr"/>
+      <c r="D378" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="E378" s="11" t="n">
+      <c r="E378" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F378" s="11" t="n">
+      <c r="F378" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="G378" s="13" t="n">
+      <c r="G378" s="12" t="n">
         <v>-0.7455435766354376</v>
       </c>
-      <c r="H378" s="13" t="n">
+      <c r="H378" s="12" t="n">
         <v>0.559702967908031</v>
       </c>
-      <c r="I378" s="13" t="n">
+      <c r="I378" s="12" t="n">
         <v>1.477709608139679</v>
       </c>
-      <c r="J378" s="13" t="n">
+      <c r="J378" s="12" t="n">
         <v>1.818276730110056</v>
       </c>
-      <c r="K378" s="13" t="n">
+      <c r="K378" s="12" t="n">
         <v>1.777438720425048</v>
       </c>
-      <c r="L378" s="13" t="n">
+      <c r="L378" s="12" t="n">
         <v>1.603903367437773</v>
       </c>
-      <c r="M378" s="11" t="inlineStr">
+      <c r="M378" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -18467,45 +18464,45 @@
       <c r="M380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="11" t="inlineStr">
+      <c r="A381" s="8" t="inlineStr">
         <is>
           <t>R0380</t>
         </is>
       </c>
-      <c r="B381" s="11" t="inlineStr">
+      <c r="B381" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C381" s="11" t="inlineStr"/>
-      <c r="D381" s="12" t="n">
+      <c r="C381" s="8" t="inlineStr"/>
+      <c r="D381" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E381" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F381" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G381" s="13" t="n">
+      <c r="E381" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F381" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G381" s="12" t="n">
         <v>0.03231870529256701</v>
       </c>
-      <c r="H381" s="13" t="n">
+      <c r="H381" s="12" t="n">
         <v>0.5345672939148693</v>
       </c>
-      <c r="I381" s="13" t="n">
+      <c r="I381" s="12" t="n">
         <v>1.451416489726839</v>
       </c>
-      <c r="J381" s="13" t="n">
+      <c r="J381" s="12" t="n">
         <v>1.747250906193196</v>
       </c>
-      <c r="K381" s="13" t="n">
+      <c r="K381" s="12" t="n">
         <v>1.685516663311448</v>
       </c>
-      <c r="L381" s="13" t="n">
+      <c r="L381" s="12" t="n">
         <v>1.841282085069512</v>
       </c>
-      <c r="M381" s="11" t="inlineStr">
+      <c r="M381" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -18635,45 +18632,45 @@
       <c r="M384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" s="11" t="inlineStr">
+      <c r="A385" s="8" t="inlineStr">
         <is>
           <t>R0384</t>
         </is>
       </c>
-      <c r="B385" s="11" t="inlineStr">
+      <c r="B385" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C385" s="11" t="inlineStr"/>
-      <c r="D385" s="12" t="n">
+      <c r="C385" s="8" t="inlineStr"/>
+      <c r="D385" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E385" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F385" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G385" s="13" t="n">
+      <c r="E385" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F385" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G385" s="12" t="n">
         <v>-1.770726266875631</v>
       </c>
-      <c r="H385" s="13" t="n">
+      <c r="H385" s="12" t="n">
         <v>0.6256719570572363</v>
       </c>
-      <c r="I385" s="13" t="n">
+      <c r="I385" s="12" t="n">
         <v>0.9852540061513574</v>
       </c>
-      <c r="J385" s="13" t="n">
+      <c r="J385" s="12" t="n">
         <v>0.05590385913143165</v>
       </c>
-      <c r="K385" s="13" t="n">
+      <c r="K385" s="12" t="n">
         <v>1.519807926123925</v>
       </c>
-      <c r="L385" s="13" t="n">
+      <c r="L385" s="12" t="n">
         <v>0.8434137452337549</v>
       </c>
-      <c r="M385" s="11" t="inlineStr">
+      <c r="M385" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -18926,45 +18923,45 @@
       <c r="M391" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" s="11" t="inlineStr">
+      <c r="A392" s="8" t="inlineStr">
         <is>
           <t>R0391</t>
         </is>
       </c>
-      <c r="B392" s="11" t="inlineStr">
+      <c r="B392" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C392" s="11" t="inlineStr"/>
-      <c r="D392" s="12" t="n">
+      <c r="C392" s="8" t="inlineStr"/>
+      <c r="D392" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E392" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F392" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G392" s="13" t="n">
+      <c r="E392" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F392" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G392" s="12" t="n">
         <v>-0.2875286259229239</v>
       </c>
-      <c r="H392" s="13" t="n">
+      <c r="H392" s="12" t="n">
         <v>0.525128174663108</v>
       </c>
-      <c r="I392" s="13" t="n">
+      <c r="I392" s="12" t="n">
         <v>1.381298057004633</v>
       </c>
-      <c r="J392" s="13" t="n">
+      <c r="J392" s="12" t="n">
         <v>1.526294999885523</v>
       </c>
-      <c r="K392" s="13" t="n">
+      <c r="K392" s="12" t="n">
         <v>1.655450835364265</v>
       </c>
-      <c r="L392" s="13" t="n">
+      <c r="L392" s="12" t="n">
         <v>1.726348235901182</v>
       </c>
-      <c r="M392" s="11" t="inlineStr">
+      <c r="M392" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -19012,45 +19009,45 @@
       <c r="M393" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" s="11" t="inlineStr">
+      <c r="A394" s="8" t="inlineStr">
         <is>
           <t>R0393</t>
         </is>
       </c>
-      <c r="B394" s="11" t="inlineStr">
+      <c r="B394" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C394" s="11" t="inlineStr"/>
-      <c r="D394" s="12" t="n">
+      <c r="C394" s="8" t="inlineStr"/>
+      <c r="D394" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E394" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F394" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G394" s="13" t="n">
+      <c r="E394" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F394" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G394" s="12" t="n">
         <v>1.83438499511204</v>
       </c>
-      <c r="H394" s="13" t="n">
+      <c r="H394" s="12" t="n">
         <v>0.6237713435108156</v>
       </c>
-      <c r="I394" s="13" t="n">
+      <c r="I394" s="12" t="n">
         <v>0.5617236292943095</v>
       </c>
-      <c r="J394" s="13" t="n">
+      <c r="J394" s="12" t="n">
         <v>-1.513355582742781</v>
       </c>
-      <c r="K394" s="13" t="n">
+      <c r="K394" s="12" t="n">
         <v>0.3370571570601545</v>
       </c>
-      <c r="L394" s="13" t="n">
+      <c r="L394" s="12" t="n">
         <v>-0.9814188910668151</v>
       </c>
-      <c r="M394" s="11" t="inlineStr">
+      <c r="M394" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -19508,45 +19505,45 @@
       <c r="M405" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="11" t="inlineStr">
+      <c r="A406" s="8" t="inlineStr">
         <is>
           <t>R0405</t>
         </is>
       </c>
-      <c r="B406" s="11" t="inlineStr">
+      <c r="B406" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C406" s="11" t="inlineStr"/>
-      <c r="D406" s="12" t="n">
+      <c r="C406" s="8" t="inlineStr"/>
+      <c r="D406" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="E406" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F406" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G406" s="13" t="n">
+      <c r="E406" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F406" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G406" s="12" t="n">
         <v>-0.5655280740349018</v>
       </c>
-      <c r="H406" s="13" t="n">
+      <c r="H406" s="12" t="n">
         <v>0.5301142963227143</v>
       </c>
-      <c r="I406" s="13" t="n">
+      <c r="I406" s="12" t="n">
         <v>1.322231558848107</v>
       </c>
-      <c r="J406" s="13" t="n">
+      <c r="J406" s="12" t="n">
         <v>1.315689145697611</v>
       </c>
-      <c r="K406" s="13" t="n">
+      <c r="K406" s="12" t="n">
         <v>1.719051874703624</v>
       </c>
-      <c r="L406" s="13" t="n">
+      <c r="L406" s="12" t="n">
         <v>1.700389262584003</v>
       </c>
-      <c r="M406" s="11" t="inlineStr">
+      <c r="M406" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -19676,45 +19673,45 @@
       <c r="M409" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" s="11" t="inlineStr">
+      <c r="A410" s="8" t="inlineStr">
         <is>
           <t>R0409</t>
         </is>
       </c>
-      <c r="B410" s="11" t="inlineStr">
+      <c r="B410" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C410" s="11" t="inlineStr"/>
-      <c r="D410" s="12" t="n">
+      <c r="C410" s="8" t="inlineStr"/>
+      <c r="D410" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E410" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F410" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G410" s="13" t="n">
+      <c r="E410" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F410" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G410" s="12" t="n">
         <v>-1.328485763496242</v>
       </c>
-      <c r="H410" s="13" t="n">
+      <c r="H410" s="12" t="n">
         <v>0.5919933833871781</v>
       </c>
-      <c r="I410" s="13" t="n">
+      <c r="I410" s="12" t="n">
         <v>0.5693520442151928</v>
       </c>
-      <c r="J410" s="13" t="n">
+      <c r="J410" s="12" t="n">
         <v>-1.685189524022549</v>
       </c>
-      <c r="K410" s="13" t="n">
+      <c r="K410" s="12" t="n">
         <v>0.4061397491308364</v>
       </c>
-      <c r="L410" s="13" t="n">
+      <c r="L410" s="12" t="n">
         <v>-1.102439346050782</v>
       </c>
-      <c r="M410" s="11" t="inlineStr">
+      <c r="M410" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -19967,135 +19964,135 @@
       <c r="M416" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" s="11" t="inlineStr">
+      <c r="A417" s="8" t="inlineStr">
         <is>
           <t>R0416</t>
         </is>
       </c>
-      <c r="B417" s="11" t="inlineStr">
+      <c r="B417" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C417" s="11" t="inlineStr"/>
-      <c r="D417" s="12" t="n">
+      <c r="C417" s="8" t="inlineStr"/>
+      <c r="D417" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E417" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F417" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G417" s="13" t="n">
+      <c r="E417" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F417" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G417" s="12" t="n">
         <v>2.258651488166693</v>
       </c>
-      <c r="H417" s="13" t="n">
+      <c r="H417" s="12" t="n">
         <v>0.6836617924804415</v>
       </c>
-      <c r="I417" s="13" t="n">
+      <c r="I417" s="12" t="n">
         <v>1.056926801423819</v>
       </c>
-      <c r="J417" s="13" t="n">
+      <c r="J417" s="12" t="n">
         <v>0.2733673672995702</v>
       </c>
-      <c r="K417" s="13" t="n">
+      <c r="K417" s="12" t="n">
         <v>1.65578709664702</v>
       </c>
-      <c r="L417" s="13" t="n">
+      <c r="L417" s="12" t="n">
         <v>0.8980086679262465</v>
       </c>
-      <c r="M417" s="11" t="inlineStr">
+      <c r="M417" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="11" t="inlineStr">
+      <c r="A418" s="8" t="inlineStr">
         <is>
           <t>R0417</t>
         </is>
       </c>
-      <c r="B418" s="11" t="inlineStr">
+      <c r="B418" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C418" s="11" t="inlineStr"/>
-      <c r="D418" s="12" t="n">
+      <c r="C418" s="8" t="inlineStr"/>
+      <c r="D418" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E418" s="11" t="n">
+      <c r="E418" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F418" s="11" t="n">
+      <c r="F418" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="G418" s="13" t="n">
+      <c r="G418" s="12" t="n">
         <v>-0.8819378635971009</v>
       </c>
-      <c r="H418" s="13" t="n">
+      <c r="H418" s="12" t="n">
         <v>0.5640910679388361</v>
       </c>
-      <c r="I418" s="13" t="n">
+      <c r="I418" s="12" t="n">
         <v>1.072074310434762</v>
       </c>
-      <c r="J418" s="13" t="n">
+      <c r="J418" s="12" t="n">
         <v>0.3718585989162594</v>
       </c>
-      <c r="K418" s="13" t="n">
+      <c r="K418" s="12" t="n">
         <v>1.836961548259272</v>
       </c>
-      <c r="L418" s="13" t="n">
+      <c r="L418" s="12" t="n">
         <v>1.602119188492594</v>
       </c>
-      <c r="M418" s="11" t="inlineStr">
+      <c r="M418" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="11" t="inlineStr">
+      <c r="A419" s="8" t="inlineStr">
         <is>
           <t>R0418</t>
         </is>
       </c>
-      <c r="B419" s="11" t="inlineStr">
+      <c r="B419" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C419" s="11" t="inlineStr"/>
-      <c r="D419" s="12" t="n">
+      <c r="C419" s="8" t="inlineStr"/>
+      <c r="D419" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E419" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F419" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G419" s="13" t="n">
+      <c r="E419" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F419" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G419" s="12" t="n">
         <v>-1.828758139764982</v>
       </c>
-      <c r="H419" s="13" t="n">
+      <c r="H419" s="12" t="n">
         <v>0.6172109748082045</v>
       </c>
-      <c r="I419" s="13" t="n">
+      <c r="I419" s="12" t="n">
         <v>0.6855873576323044</v>
       </c>
-      <c r="J419" s="13" t="n">
+      <c r="J419" s="12" t="n">
         <v>-1.010475920848466</v>
       </c>
-      <c r="K419" s="13" t="n">
+      <c r="K419" s="12" t="n">
         <v>0.4209977721132823</v>
       </c>
-      <c r="L419" s="13" t="n">
+      <c r="L419" s="12" t="n">
         <v>-0.7445682431191821</v>
       </c>
-      <c r="M419" s="11" t="inlineStr">
+      <c r="M419" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -20348,45 +20345,45 @@
       <c r="M425" t="inlineStr"/>
     </row>
     <row r="426">
-      <c r="A426" s="11" t="inlineStr">
+      <c r="A426" s="8" t="inlineStr">
         <is>
           <t>R0425</t>
         </is>
       </c>
-      <c r="B426" s="11" t="inlineStr">
+      <c r="B426" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C426" s="11" t="inlineStr"/>
-      <c r="D426" s="12" t="n">
+      <c r="C426" s="8" t="inlineStr"/>
+      <c r="D426" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E426" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F426" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G426" s="13" t="n">
+      <c r="E426" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F426" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G426" s="12" t="n">
         <v>1.140817678674626</v>
       </c>
-      <c r="H426" s="13" t="n">
+      <c r="H426" s="12" t="n">
         <v>0.5618791360218677</v>
       </c>
-      <c r="I426" s="13" t="n">
+      <c r="I426" s="12" t="n">
         <v>1.046624138472083</v>
       </c>
-      <c r="J426" s="13" t="n">
+      <c r="J426" s="12" t="n">
         <v>0.2591811702697743</v>
       </c>
-      <c r="K426" s="13" t="n">
+      <c r="K426" s="12" t="n">
         <v>1.56780983285282</v>
       </c>
-      <c r="L426" s="13" t="n">
+      <c r="L426" s="12" t="n">
         <v>1.136087538720206</v>
       </c>
-      <c r="M426" s="11" t="inlineStr">
+      <c r="M426" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -20434,45 +20431,45 @@
       <c r="M427" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" s="11" t="inlineStr">
+      <c r="A428" s="8" t="inlineStr">
         <is>
           <t>R0427</t>
         </is>
       </c>
-      <c r="B428" s="11" t="inlineStr">
+      <c r="B428" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C428" s="11" t="inlineStr"/>
-      <c r="D428" s="12" t="n">
+      <c r="C428" s="8" t="inlineStr"/>
+      <c r="D428" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E428" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F428" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G428" s="13" t="n">
+      <c r="E428" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F428" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G428" s="12" t="n">
         <v>1.774864286763018</v>
       </c>
-      <c r="H428" s="13" t="n">
+      <c r="H428" s="12" t="n">
         <v>0.6328363867974932</v>
       </c>
-      <c r="I428" s="13" t="n">
+      <c r="I428" s="12" t="n">
         <v>0.5604837007618924</v>
       </c>
-      <c r="J428" s="13" t="n">
+      <c r="J428" s="12" t="n">
         <v>-1.547521697521466</v>
       </c>
-      <c r="K428" s="13" t="n">
+      <c r="K428" s="12" t="n">
         <v>0.3409590152637234</v>
       </c>
-      <c r="L428" s="13" t="n">
+      <c r="L428" s="12" t="n">
         <v>-0.9575281071580087</v>
       </c>
-      <c r="M428" s="11" t="inlineStr">
+      <c r="M428" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -20561,45 +20558,45 @@
       <c r="M430" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" s="11" t="inlineStr">
+      <c r="A431" s="8" t="inlineStr">
         <is>
           <t>R0430</t>
         </is>
       </c>
-      <c r="B431" s="11" t="inlineStr">
+      <c r="B431" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C431" s="11" t="inlineStr"/>
-      <c r="D431" s="12" t="n">
+      <c r="C431" s="8" t="inlineStr"/>
+      <c r="D431" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="E431" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F431" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G431" s="13" t="n">
+      <c r="E431" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F431" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G431" s="12" t="n">
         <v>0.263375923455839</v>
       </c>
-      <c r="H431" s="13" t="n">
+      <c r="H431" s="12" t="n">
         <v>0.5270972683902927</v>
       </c>
-      <c r="I431" s="13" t="n">
+      <c r="I431" s="12" t="n">
         <v>0.4960164776763633</v>
       </c>
-      <c r="J431" s="13" t="n">
+      <c r="J431" s="12" t="n">
         <v>-2.484641992699929</v>
       </c>
-      <c r="K431" s="13" t="n">
+      <c r="K431" s="12" t="n">
         <v>0.4177713011116535</v>
       </c>
-      <c r="L431" s="13" t="n">
+      <c r="L431" s="12" t="n">
         <v>-2.146872972021708</v>
       </c>
-      <c r="M431" s="11" t="inlineStr">
+      <c r="M431" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -20852,45 +20849,45 @@
       <c r="M437" t="inlineStr"/>
     </row>
     <row r="438">
-      <c r="A438" s="11" t="inlineStr">
+      <c r="A438" s="8" t="inlineStr">
         <is>
           <t>R0437</t>
         </is>
       </c>
-      <c r="B438" s="11" t="inlineStr">
+      <c r="B438" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C438" s="11" t="inlineStr"/>
-      <c r="D438" s="12" t="n">
+      <c r="C438" s="8" t="inlineStr"/>
+      <c r="D438" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="E438" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F438" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G438" s="13" t="n">
+      <c r="E438" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F438" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G438" s="12" t="n">
         <v>0.2633759234558391</v>
       </c>
-      <c r="H438" s="13" t="n">
+      <c r="H438" s="12" t="n">
         <v>0.5270972683902927</v>
       </c>
-      <c r="I438" s="13" t="n">
+      <c r="I438" s="12" t="n">
         <v>0.5437337465534799</v>
       </c>
-      <c r="J438" s="13" t="n">
+      <c r="J438" s="12" t="n">
         <v>-2.181647982406334</v>
       </c>
-      <c r="K438" s="13" t="n">
+      <c r="K438" s="12" t="n">
         <v>0.4523818021200015</v>
       </c>
-      <c r="L438" s="13" t="n">
+      <c r="L438" s="12" t="n">
         <v>-1.96704415069396</v>
       </c>
-      <c r="M438" s="11" t="inlineStr">
+      <c r="M438" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -21102,90 +21099,90 @@
       <c r="M443" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" s="11" t="inlineStr">
+      <c r="A444" s="8" t="inlineStr">
         <is>
           <t>R0443</t>
         </is>
       </c>
-      <c r="B444" s="11" t="inlineStr">
+      <c r="B444" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C444" s="11" t="inlineStr"/>
-      <c r="D444" s="12" t="n">
+      <c r="C444" s="8" t="inlineStr"/>
+      <c r="D444" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E444" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F444" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G444" s="13" t="n">
+      <c r="E444" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F444" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G444" s="12" t="n">
         <v>-1.043172599859802</v>
       </c>
-      <c r="H444" s="13" t="n">
+      <c r="H444" s="12" t="n">
         <v>0.5691969224136079</v>
       </c>
-      <c r="I444" s="13" t="n">
+      <c r="I444" s="12" t="n">
         <v>0.5626690012728114</v>
       </c>
-      <c r="J444" s="13" t="n">
+      <c r="J444" s="12" t="n">
         <v>-1.892321927899348</v>
       </c>
-      <c r="K444" s="13" t="n">
+      <c r="K444" s="12" t="n">
         <v>0.4226126999959043</v>
       </c>
-      <c r="L444" s="13" t="n">
+      <c r="L444" s="12" t="n">
         <v>-1.306159825213314</v>
       </c>
-      <c r="M444" s="11" t="inlineStr">
+      <c r="M444" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="11" t="inlineStr">
+      <c r="A445" s="8" t="inlineStr">
         <is>
           <t>R0444</t>
         </is>
       </c>
-      <c r="B445" s="11" t="inlineStr">
+      <c r="B445" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C445" s="11" t="inlineStr"/>
-      <c r="D445" s="12" t="n">
+      <c r="C445" s="8" t="inlineStr"/>
+      <c r="D445" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E445" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F445" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G445" s="13" t="n">
+      <c r="E445" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F445" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G445" s="12" t="n">
         <v>-2.244923279930266</v>
       </c>
-      <c r="H445" s="13" t="n">
+      <c r="H445" s="12" t="n">
         <v>0.677792449111126</v>
       </c>
-      <c r="I445" s="13" t="n">
+      <c r="I445" s="12" t="n">
         <v>0.8648220988372397</v>
       </c>
-      <c r="J445" s="13" t="n">
+      <c r="J445" s="12" t="n">
         <v>-0.2341454887982257</v>
       </c>
-      <c r="K445" s="13" t="n">
+      <c r="K445" s="12" t="n">
         <v>0.4753544818084068</v>
       </c>
-      <c r="L445" s="13" t="n">
+      <c r="L445" s="12" t="n">
         <v>-0.3776248013913959</v>
       </c>
-      <c r="M445" s="11" t="inlineStr">
+      <c r="M445" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -21643,45 +21640,45 @@
       <c r="M456" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" s="11" t="inlineStr">
+      <c r="A457" s="8" t="inlineStr">
         <is>
           <t>R0456</t>
         </is>
       </c>
-      <c r="B457" s="11" t="inlineStr">
+      <c r="B457" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C457" s="11" t="inlineStr"/>
-      <c r="D457" s="12" t="n">
+      <c r="C457" s="8" t="inlineStr"/>
+      <c r="D457" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E457" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F457" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G457" s="13" t="n">
+      <c r="E457" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F457" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G457" s="12" t="n">
         <v>1.444044146311112</v>
       </c>
-      <c r="H457" s="13" t="n">
+      <c r="H457" s="12" t="n">
         <v>0.5913840969234762</v>
       </c>
-      <c r="I457" s="13" t="n">
+      <c r="I457" s="12" t="n">
         <v>1.302724377123915</v>
       </c>
-      <c r="J457" s="13" t="n">
+      <c r="J457" s="12" t="n">
         <v>1.062122267557004</v>
       </c>
-      <c r="K457" s="13" t="n">
+      <c r="K457" s="12" t="n">
         <v>1.825109273385824</v>
       </c>
-      <c r="L457" s="13" t="n">
+      <c r="L457" s="12" t="n">
         <v>1.306175067031297</v>
       </c>
-      <c r="M457" s="11" t="inlineStr">
+      <c r="M457" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -22221,45 +22218,45 @@
       <c r="M470" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" s="11" t="inlineStr">
+      <c r="A471" s="8" t="inlineStr">
         <is>
           <t>R0470</t>
         </is>
       </c>
-      <c r="B471" s="11" t="inlineStr">
+      <c r="B471" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C471" s="11" t="inlineStr"/>
-      <c r="D471" s="12" t="n">
+      <c r="C471" s="8" t="inlineStr"/>
+      <c r="D471" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="E471" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F471" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G471" s="13" t="n">
+      <c r="E471" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F471" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G471" s="12" t="n">
         <v>0.5444335812258353</v>
       </c>
-      <c r="H471" s="13" t="n">
+      <c r="H471" s="12" t="n">
         <v>0.5338858410554059</v>
       </c>
-      <c r="I471" s="13" t="n">
+      <c r="I471" s="12" t="n">
         <v>0.5045119429561051</v>
       </c>
-      <c r="J471" s="13" t="n">
+      <c r="J471" s="12" t="n">
         <v>-2.349702932407293</v>
       </c>
-      <c r="K471" s="13" t="n">
+      <c r="K471" s="12" t="n">
         <v>0.4168164092905916</v>
       </c>
-      <c r="L471" s="13" t="n">
+      <c r="L471" s="12" t="n">
         <v>-1.939633216318067</v>
       </c>
-      <c r="M471" s="11" t="inlineStr">
+      <c r="M471" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -22389,90 +22386,90 @@
       <c r="M474" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" s="11" t="inlineStr">
+      <c r="A475" s="8" t="inlineStr">
         <is>
           <t>R0474</t>
         </is>
       </c>
-      <c r="B475" s="11" t="inlineStr">
+      <c r="B475" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C475" s="11" t="inlineStr"/>
-      <c r="D475" s="12" t="n">
+      <c r="C475" s="8" t="inlineStr"/>
+      <c r="D475" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="E475" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F475" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G475" s="13" t="n">
+      <c r="E475" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F475" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G475" s="12" t="n">
         <v>2.795636414735082</v>
       </c>
-      <c r="H475" s="13" t="n">
+      <c r="H475" s="12" t="n">
         <v>0.7930629618978372</v>
       </c>
-      <c r="I475" s="13" t="n">
+      <c r="I475" s="12" t="n">
         <v>1.371900561766172</v>
       </c>
-      <c r="J475" s="13" t="n">
+      <c r="J475" s="12" t="n">
         <v>0.8146351021145593</v>
       </c>
-      <c r="K475" s="13" t="n">
+      <c r="K475" s="12" t="n">
         <v>1.990385626163997</v>
       </c>
-      <c r="L475" s="13" t="n">
+      <c r="L475" s="12" t="n">
         <v>1.035460948870191</v>
       </c>
-      <c r="M475" s="11" t="inlineStr">
+      <c r="M475" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="11" t="inlineStr">
+      <c r="A476" s="8" t="inlineStr">
         <is>
           <t>R0475</t>
         </is>
       </c>
-      <c r="B476" s="11" t="inlineStr">
+      <c r="B476" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C476" s="11" t="inlineStr"/>
-      <c r="D476" s="12" t="n">
+      <c r="C476" s="8" t="inlineStr"/>
+      <c r="D476" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="E476" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F476" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G476" s="13" t="n">
+      <c r="E476" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F476" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G476" s="12" t="n">
         <v>1.091520892548687</v>
       </c>
-      <c r="H476" s="13" t="n">
+      <c r="H476" s="12" t="n">
         <v>0.5707173397218593</v>
       </c>
-      <c r="I476" s="13" t="n">
+      <c r="I476" s="12" t="n">
         <v>0.6208663746308793</v>
       </c>
-      <c r="J476" s="13" t="n">
+      <c r="J476" s="12" t="n">
         <v>-1.538289829999081</v>
       </c>
-      <c r="K476" s="13" t="n">
+      <c r="K476" s="12" t="n">
         <v>0.4861708576464879</v>
       </c>
-      <c r="L476" s="13" t="n">
+      <c r="L476" s="12" t="n">
         <v>-1.107619815277253</v>
       </c>
-      <c r="M476" s="11" t="inlineStr">
+      <c r="M476" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -22520,45 +22517,45 @@
       <c r="M477" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" s="11" t="inlineStr">
+      <c r="A478" s="8" t="inlineStr">
         <is>
           <t>R0477</t>
         </is>
       </c>
-      <c r="B478" s="11" t="inlineStr">
+      <c r="B478" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C478" s="11" t="inlineStr"/>
-      <c r="D478" s="12" t="n">
+      <c r="C478" s="8" t="inlineStr"/>
+      <c r="D478" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E478" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F478" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G478" s="13" t="n">
+      <c r="E478" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F478" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G478" s="12" t="n">
         <v>1.140817678674626</v>
       </c>
-      <c r="H478" s="13" t="n">
+      <c r="H478" s="12" t="n">
         <v>0.5618791360218677</v>
       </c>
-      <c r="I478" s="13" t="n">
+      <c r="I478" s="12" t="n">
         <v>0.5672445066789999</v>
       </c>
-      <c r="J478" s="13" t="n">
+      <c r="J478" s="12" t="n">
         <v>-1.800946434820856</v>
       </c>
-      <c r="K478" s="13" t="n">
+      <c r="K478" s="12" t="n">
         <v>0.4265517371444459</v>
       </c>
-      <c r="L478" s="13" t="n">
+      <c r="L478" s="12" t="n">
         <v>-1.315040180100433</v>
       </c>
-      <c r="M478" s="11" t="inlineStr">
+      <c r="M478" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -22729,45 +22726,45 @@
       <c r="M482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" s="11" t="inlineStr">
+      <c r="A483" s="8" t="inlineStr">
         <is>
           <t>R0482</t>
         </is>
       </c>
-      <c r="B483" s="11" t="inlineStr">
+      <c r="B483" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C483" s="11" t="inlineStr"/>
-      <c r="D483" s="12" t="n">
+      <c r="C483" s="8" t="inlineStr"/>
+      <c r="D483" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E483" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F483" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G483" s="13" t="n">
+      <c r="E483" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F483" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G483" s="12" t="n">
         <v>2.258651488166693</v>
       </c>
-      <c r="H483" s="13" t="n">
+      <c r="H483" s="12" t="n">
         <v>0.6836617924804415</v>
       </c>
-      <c r="I483" s="13" t="n">
+      <c r="I483" s="12" t="n">
         <v>1.323530979760131</v>
       </c>
-      <c r="J483" s="13" t="n">
+      <c r="J483" s="12" t="n">
         <v>0.8872136554370835</v>
       </c>
-      <c r="K483" s="13" t="n">
+      <c r="K483" s="12" t="n">
         <v>2.023955965179911</v>
       </c>
-      <c r="L483" s="13" t="n">
+      <c r="L483" s="12" t="n">
         <v>1.159815688614358</v>
       </c>
-      <c r="M483" s="11" t="inlineStr">
+      <c r="M483" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -22815,45 +22812,45 @@
       <c r="M484" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" s="11" t="inlineStr">
+      <c r="A485" s="8" t="inlineStr">
         <is>
           <t>R0484</t>
         </is>
       </c>
-      <c r="B485" s="11" t="inlineStr">
+      <c r="B485" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C485" s="11" t="inlineStr"/>
-      <c r="D485" s="12" t="n">
+      <c r="C485" s="8" t="inlineStr"/>
+      <c r="D485" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="E485" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F485" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G485" s="13" t="n">
+      <c r="E485" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F485" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G485" s="12" t="n">
         <v>1.039751408414977</v>
       </c>
-      <c r="H485" s="13" t="n">
+      <c r="H485" s="12" t="n">
         <v>0.575521132050015</v>
       </c>
-      <c r="I485" s="13" t="n">
+      <c r="I485" s="12" t="n">
         <v>1.335753003860712</v>
       </c>
-      <c r="J485" s="13" t="n">
+      <c r="J485" s="12" t="n">
         <v>1.168359158438293</v>
       </c>
-      <c r="K485" s="13" t="n">
+      <c r="K485" s="12" t="n">
         <v>2.715347580073009</v>
       </c>
-      <c r="L485" s="13" t="n">
+      <c r="L485" s="12" t="n">
         <v>2.554276381776936</v>
       </c>
-      <c r="M485" s="11" t="inlineStr">
+      <c r="M485" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -23311,45 +23308,45 @@
       <c r="M496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" s="11" t="inlineStr">
+      <c r="A497" s="8" t="inlineStr">
         <is>
           <t>R0496</t>
         </is>
       </c>
-      <c r="B497" s="11" t="inlineStr">
+      <c r="B497" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C497" s="11" t="inlineStr"/>
-      <c r="D497" s="12" t="n">
+      <c r="C497" s="8" t="inlineStr"/>
+      <c r="D497" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E497" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F497" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G497" s="13" t="n">
+      <c r="E497" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F497" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G497" s="12" t="n">
         <v>1.140817678674626</v>
       </c>
-      <c r="H497" s="13" t="n">
+      <c r="H497" s="12" t="n">
         <v>0.5618791360218677</v>
       </c>
-      <c r="I497" s="13" t="n">
+      <c r="I497" s="12" t="n">
         <v>1.124458897343453</v>
       </c>
-      <c r="J497" s="13" t="n">
+      <c r="J497" s="12" t="n">
         <v>0.5291178051283809</v>
       </c>
-      <c r="K497" s="13" t="n">
+      <c r="K497" s="12" t="n">
         <v>1.546113061837162</v>
       </c>
-      <c r="L497" s="13" t="n">
+      <c r="L497" s="12" t="n">
         <v>1.103818253019522</v>
       </c>
-      <c r="M497" s="11" t="inlineStr">
+      <c r="M497" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -23438,82 +23435,82 @@
       <c r="M499" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" s="14" t="inlineStr">
+      <c r="A500" s="13" t="inlineStr">
         <is>
           <t>R0499</t>
         </is>
       </c>
-      <c r="B500" s="14" t="inlineStr">
+      <c r="B500" s="13" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C500" s="14" t="inlineStr">
-        <is>
-          <t>ekstrem maksimum</t>
-        </is>
-      </c>
-      <c r="D500" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="E500" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="F500" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="G500" s="16" t="n">
+      <c r="C500" s="13" t="inlineStr">
+        <is>
+          <t>Extreme (maximum)</t>
+        </is>
+      </c>
+      <c r="D500" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E500" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F500" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G500" s="15" t="n">
         <v>4.904685185437006</v>
       </c>
-      <c r="H500" s="16" t="n">
+      <c r="H500" s="15" t="n">
         <v>1.858397119524021</v>
       </c>
-      <c r="I500" s="14" t="n"/>
-      <c r="J500" s="14" t="n"/>
-      <c r="K500" s="14" t="n"/>
-      <c r="L500" s="14" t="n"/>
-      <c r="M500" s="14" t="inlineStr"/>
+      <c r="I500" s="13" t="n"/>
+      <c r="J500" s="13" t="n"/>
+      <c r="K500" s="13" t="n"/>
+      <c r="L500" s="13" t="n"/>
+      <c r="M500" s="13" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" s="11" t="inlineStr">
+      <c r="A501" s="8" t="inlineStr">
         <is>
           <t>R0500</t>
         </is>
       </c>
-      <c r="B501" s="11" t="inlineStr">
+      <c r="B501" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C501" s="11" t="inlineStr"/>
-      <c r="D501" s="12" t="n">
+      <c r="C501" s="8" t="inlineStr"/>
+      <c r="D501" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="E501" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F501" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G501" s="13" t="n">
+      <c r="E501" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F501" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G501" s="12" t="n">
         <v>-0.379716294090137</v>
       </c>
-      <c r="H501" s="13" t="n">
+      <c r="H501" s="12" t="n">
         <v>0.5433104041616064</v>
       </c>
-      <c r="I501" s="13" t="n">
+      <c r="I501" s="12" t="n">
         <v>0.4921118695029126</v>
       </c>
-      <c r="J501" s="13" t="n">
+      <c r="J501" s="12" t="n">
         <v>-2.478226913409788</v>
       </c>
-      <c r="K501" s="13" t="n">
+      <c r="K501" s="12" t="n">
         <v>0.40903650902923</v>
       </c>
-      <c r="L501" s="13" t="n">
+      <c r="L501" s="12" t="n">
         <v>-1.985724012011548</v>
       </c>
-      <c r="M501" s="11" t="inlineStr">
+      <c r="M501" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -23602,90 +23599,90 @@
       <c r="M503" t="inlineStr"/>
     </row>
     <row r="504">
-      <c r="A504" s="11" t="inlineStr">
+      <c r="A504" s="8" t="inlineStr">
         <is>
           <t>R0503</t>
         </is>
       </c>
-      <c r="B504" s="11" t="inlineStr">
+      <c r="B504" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C504" s="11" t="inlineStr"/>
-      <c r="D504" s="12" t="n">
+      <c r="C504" s="8" t="inlineStr"/>
+      <c r="D504" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E504" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F504" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G504" s="13" t="n">
+      <c r="E504" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F504" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G504" s="12" t="n">
         <v>-2.749307339212922</v>
       </c>
-      <c r="H504" s="13" t="n">
+      <c r="H504" s="12" t="n">
         <v>0.7915943701020112</v>
       </c>
-      <c r="I504" s="13" t="n">
+      <c r="I504" s="12" t="n">
         <v>0.7255214132017517</v>
       </c>
-      <c r="J504" s="13" t="n">
+      <c r="J504" s="12" t="n">
         <v>-0.412484544214525</v>
       </c>
-      <c r="K504" s="13" t="n">
+      <c r="K504" s="12" t="n">
         <v>0.3254060691593724</v>
       </c>
-      <c r="L504" s="13" t="n">
+      <c r="L504" s="12" t="n">
         <v>-0.3000408938364186</v>
       </c>
-      <c r="M504" s="11" t="inlineStr">
+      <c r="M504" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="11" t="inlineStr">
+      <c r="A505" s="8" t="inlineStr">
         <is>
           <t>R0504</t>
         </is>
       </c>
-      <c r="B505" s="11" t="inlineStr">
+      <c r="B505" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C505" s="11" t="inlineStr"/>
-      <c r="D505" s="12" t="n">
+      <c r="C505" s="8" t="inlineStr"/>
+      <c r="D505" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E505" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F505" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G505" s="13" t="n">
+      <c r="E505" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F505" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G505" s="12" t="n">
         <v>-1.828758139764982</v>
       </c>
-      <c r="H505" s="13" t="n">
+      <c r="H505" s="12" t="n">
         <v>0.6172109748082045</v>
       </c>
-      <c r="I505" s="13" t="n">
+      <c r="I505" s="12" t="n">
         <v>0.7419101873440854</v>
       </c>
-      <c r="J505" s="13" t="n">
+      <c r="J505" s="12" t="n">
         <v>-0.7884506779180868</v>
       </c>
-      <c r="K505" s="13" t="n">
+      <c r="K505" s="12" t="n">
         <v>0.4876427501247642</v>
       </c>
-      <c r="L505" s="13" t="n">
+      <c r="L505" s="12" t="n">
         <v>-0.5949603453557971</v>
       </c>
-      <c r="M505" s="11" t="inlineStr">
+      <c r="M505" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -23815,45 +23812,45 @@
       <c r="M508" t="inlineStr"/>
     </row>
     <row r="509">
-      <c r="A509" s="11" t="inlineStr">
+      <c r="A509" s="8" t="inlineStr">
         <is>
           <t>R0508</t>
         </is>
       </c>
-      <c r="B509" s="11" t="inlineStr">
+      <c r="B509" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C509" s="11" t="inlineStr"/>
-      <c r="D509" s="12" t="n">
+      <c r="C509" s="8" t="inlineStr"/>
+      <c r="D509" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E509" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F509" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G509" s="13" t="n">
+      <c r="E509" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F509" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G509" s="12" t="n">
         <v>-0.1181880204111045</v>
       </c>
-      <c r="H509" s="13" t="n">
+      <c r="H509" s="12" t="n">
         <v>0.5420180209508564</v>
       </c>
-      <c r="I509" s="13" t="n">
+      <c r="I509" s="12" t="n">
         <v>1.830044802588576</v>
       </c>
-      <c r="J509" s="13" t="n">
+      <c r="J509" s="12" t="n">
         <v>2.750246085205753</v>
       </c>
-      <c r="K509" s="13" t="n">
+      <c r="K509" s="12" t="n">
         <v>2.140691859088895</v>
       </c>
-      <c r="L509" s="13" t="n">
+      <c r="L509" s="12" t="n">
         <v>2.625515883348092</v>
       </c>
-      <c r="M509" s="11" t="inlineStr">
+      <c r="M509" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -23901,45 +23898,45 @@
       <c r="M510" t="inlineStr"/>
     </row>
     <row r="511">
-      <c r="A511" s="11" t="inlineStr">
+      <c r="A511" s="8" t="inlineStr">
         <is>
           <t>R0510</t>
         </is>
       </c>
-      <c r="B511" s="11" t="inlineStr">
+      <c r="B511" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C511" s="11" t="inlineStr"/>
-      <c r="D511" s="12" t="n">
+      <c r="C511" s="8" t="inlineStr"/>
+      <c r="D511" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E511" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F511" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G511" s="13" t="n">
+      <c r="E511" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F511" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G511" s="12" t="n">
         <v>-2.774157390045823</v>
       </c>
-      <c r="H511" s="13" t="n">
+      <c r="H511" s="12" t="n">
         <v>0.7883472621162863</v>
       </c>
-      <c r="I511" s="13" t="n">
+      <c r="I511" s="12" t="n">
         <v>1.143590574560207</v>
       </c>
-      <c r="J511" s="13" t="n">
+      <c r="J511" s="12" t="n">
         <v>0.4360607476644043</v>
       </c>
-      <c r="K511" s="13" t="n">
+      <c r="K511" s="12" t="n">
         <v>4.087513182341132</v>
       </c>
-      <c r="L511" s="13" t="n">
+      <c r="L511" s="12" t="n">
         <v>1.846089532829813</v>
       </c>
-      <c r="M511" s="11" t="inlineStr">
+      <c r="M511" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -24069,41 +24066,41 @@
       <c r="M514" t="inlineStr"/>
     </row>
     <row r="515">
-      <c r="A515" s="14" t="inlineStr">
+      <c r="A515" s="13" t="inlineStr">
         <is>
           <t>R0514</t>
         </is>
       </c>
-      <c r="B515" s="14" t="inlineStr">
+      <c r="B515" s="13" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C515" s="14" t="inlineStr">
-        <is>
-          <t>ekstrem maksimum</t>
-        </is>
-      </c>
-      <c r="D515" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="E515" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="F515" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="G515" s="16" t="n">
+      <c r="C515" s="13" t="inlineStr">
+        <is>
+          <t>Extreme (maximum)</t>
+        </is>
+      </c>
+      <c r="D515" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E515" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F515" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G515" s="15" t="n">
         <v>4.904685185437006</v>
       </c>
-      <c r="H515" s="16" t="n">
+      <c r="H515" s="15" t="n">
         <v>1.858397119524021</v>
       </c>
-      <c r="I515" s="14" t="n"/>
-      <c r="J515" s="14" t="n"/>
-      <c r="K515" s="14" t="n"/>
-      <c r="L515" s="14" t="n"/>
-      <c r="M515" s="14" t="inlineStr"/>
+      <c r="I515" s="13" t="n"/>
+      <c r="J515" s="13" t="n"/>
+      <c r="K515" s="13" t="n"/>
+      <c r="L515" s="13" t="n"/>
+      <c r="M515" s="13" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -24352,45 +24349,45 @@
       <c r="M521" t="inlineStr"/>
     </row>
     <row r="522">
-      <c r="A522" s="11" t="inlineStr">
+      <c r="A522" s="8" t="inlineStr">
         <is>
           <t>R0521</t>
         </is>
       </c>
-      <c r="B522" s="11" t="inlineStr">
+      <c r="B522" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C522" s="11" t="inlineStr"/>
-      <c r="D522" s="12" t="n">
+      <c r="C522" s="8" t="inlineStr"/>
+      <c r="D522" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E522" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F522" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G522" s="13" t="n">
+      <c r="E522" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F522" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G522" s="12" t="n">
         <v>-1.828758139764982</v>
       </c>
-      <c r="H522" s="13" t="n">
+      <c r="H522" s="12" t="n">
         <v>0.6172109748082045</v>
       </c>
-      <c r="I522" s="13" t="n">
+      <c r="I522" s="12" t="n">
         <v>0.7729770901715773</v>
       </c>
-      <c r="J522" s="13" t="n">
+      <c r="J522" s="12" t="n">
         <v>-0.6707656813042028</v>
       </c>
-      <c r="K522" s="13" t="n">
+      <c r="K522" s="12" t="n">
         <v>0.4703666590773743</v>
       </c>
-      <c r="L522" s="13" t="n">
+      <c r="L522" s="12" t="n">
         <v>-0.632363368360786</v>
       </c>
-      <c r="M522" s="11" t="inlineStr">
+      <c r="M522" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -24725,45 +24722,45 @@
       <c r="M530" t="inlineStr"/>
     </row>
     <row r="531">
-      <c r="A531" s="11" t="inlineStr">
+      <c r="A531" s="8" t="inlineStr">
         <is>
           <t>R0530</t>
         </is>
       </c>
-      <c r="B531" s="11" t="inlineStr">
+      <c r="B531" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C531" s="11" t="inlineStr"/>
-      <c r="D531" s="12" t="n">
+      <c r="C531" s="8" t="inlineStr"/>
+      <c r="D531" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E531" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F531" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G531" s="13" t="n">
+      <c r="E531" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F531" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G531" s="12" t="n">
         <v>-2.774157390045823</v>
       </c>
-      <c r="H531" s="13" t="n">
+      <c r="H531" s="12" t="n">
         <v>0.7883472621162863</v>
       </c>
-      <c r="I531" s="13" t="n">
+      <c r="I531" s="12" t="n">
         <v>1.322046033666167</v>
       </c>
-      <c r="J531" s="13" t="n">
+      <c r="J531" s="12" t="n">
         <v>0.730930752373797</v>
       </c>
-      <c r="K531" s="13" t="n">
+      <c r="K531" s="12" t="n">
         <v>1.723305003111113</v>
       </c>
-      <c r="L531" s="13" t="n">
+      <c r="L531" s="12" t="n">
         <v>0.8936085536846469</v>
       </c>
-      <c r="M531" s="11" t="inlineStr">
+      <c r="M531" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -25057,45 +25054,45 @@
       <c r="M538" t="inlineStr"/>
     </row>
     <row r="539">
-      <c r="A539" s="11" t="inlineStr">
+      <c r="A539" s="8" t="inlineStr">
         <is>
           <t>R0538</t>
         </is>
       </c>
-      <c r="B539" s="11" t="inlineStr">
+      <c r="B539" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C539" s="11" t="inlineStr"/>
-      <c r="D539" s="12" t="n">
+      <c r="C539" s="8" t="inlineStr"/>
+      <c r="D539" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="E539" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F539" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G539" s="13" t="n">
+      <c r="E539" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F539" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G539" s="12" t="n">
         <v>0.8350494176261473</v>
       </c>
-      <c r="H539" s="13" t="n">
+      <c r="H539" s="12" t="n">
         <v>0.5450927213778975</v>
       </c>
-      <c r="I539" s="13" t="n">
+      <c r="I539" s="12" t="n">
         <v>0.501136748352751</v>
       </c>
-      <c r="J539" s="13" t="n">
+      <c r="J539" s="12" t="n">
         <v>-2.278015092815872</v>
       </c>
-      <c r="K539" s="13" t="n">
+      <c r="K539" s="12" t="n">
         <v>0.4032335050769499</v>
       </c>
-      <c r="L539" s="13" t="n">
+      <c r="L539" s="12" t="n">
         <v>-1.711191808322271</v>
       </c>
-      <c r="M539" s="11" t="inlineStr">
+      <c r="M539" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -25389,45 +25386,45 @@
       <c r="M546" t="inlineStr"/>
     </row>
     <row r="547">
-      <c r="A547" s="11" t="inlineStr">
+      <c r="A547" s="8" t="inlineStr">
         <is>
           <t>R0546</t>
         </is>
       </c>
-      <c r="B547" s="11" t="inlineStr">
+      <c r="B547" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C547" s="11" t="inlineStr"/>
-      <c r="D547" s="12" t="n">
+      <c r="C547" s="8" t="inlineStr"/>
+      <c r="D547" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="E547" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F547" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G547" s="13" t="n">
+      <c r="E547" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F547" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G547" s="12" t="n">
         <v>2.795636414735082</v>
       </c>
-      <c r="H547" s="13" t="n">
+      <c r="H547" s="12" t="n">
         <v>0.7930629618978372</v>
       </c>
-      <c r="I547" s="13" t="n">
+      <c r="I547" s="12" t="n">
         <v>1.410934178125583</v>
       </c>
-      <c r="J547" s="13" t="n">
+      <c r="J547" s="12" t="n">
         <v>0.8748688937118133</v>
       </c>
-      <c r="K547" s="13" t="n">
+      <c r="K547" s="12" t="n">
         <v>7.793868224259566</v>
       </c>
-      <c r="L547" s="13" t="n">
+      <c r="L547" s="12" t="n">
         <v>2.773513052031218</v>
       </c>
-      <c r="M547" s="11" t="inlineStr">
+      <c r="M547" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -25516,90 +25513,90 @@
       <c r="M549" t="inlineStr"/>
     </row>
     <row r="550">
-      <c r="A550" s="11" t="inlineStr">
+      <c r="A550" s="8" t="inlineStr">
         <is>
           <t>R0549</t>
         </is>
       </c>
-      <c r="B550" s="11" t="inlineStr">
+      <c r="B550" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C550" s="11" t="inlineStr"/>
-      <c r="D550" s="12" t="n">
+      <c r="C550" s="8" t="inlineStr"/>
+      <c r="D550" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E550" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F550" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G550" s="13" t="n">
+      <c r="E550" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F550" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G550" s="12" t="n">
         <v>1.140817678674626</v>
       </c>
-      <c r="H550" s="13" t="n">
+      <c r="H550" s="12" t="n">
         <v>0.5618791360218677</v>
       </c>
-      <c r="I550" s="13" t="n">
+      <c r="I550" s="12" t="n">
         <v>0.5832888019155827</v>
       </c>
-      <c r="J550" s="13" t="n">
+      <c r="J550" s="12" t="n">
         <v>-1.71599463144302</v>
       </c>
-      <c r="K550" s="13" t="n">
+      <c r="K550" s="12" t="n">
         <v>0.4421056592488427</v>
       </c>
-      <c r="L550" s="13" t="n">
+      <c r="L550" s="12" t="n">
         <v>-1.260853117967697</v>
       </c>
-      <c r="M550" s="11" t="inlineStr">
+      <c r="M550" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="11" t="inlineStr">
+      <c r="A551" s="8" t="inlineStr">
         <is>
           <t>R0550</t>
         </is>
       </c>
-      <c r="B551" s="11" t="inlineStr">
+      <c r="B551" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C551" s="11" t="inlineStr"/>
-      <c r="D551" s="12" t="n">
+      <c r="C551" s="8" t="inlineStr"/>
+      <c r="D551" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E551" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F551" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G551" s="13" t="n">
+      <c r="E551" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F551" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G551" s="12" t="n">
         <v>-0.01259695299819895</v>
       </c>
-      <c r="H551" s="13" t="n">
+      <c r="H551" s="12" t="n">
         <v>0.5242098425849395</v>
       </c>
-      <c r="I551" s="13" t="n">
+      <c r="I551" s="12" t="n">
         <v>0.5631265978026208</v>
       </c>
-      <c r="J551" s="13" t="n">
+      <c r="J551" s="12" t="n">
         <v>-2.115036511651223</v>
       </c>
-      <c r="K551" s="13" t="n">
+      <c r="K551" s="12" t="n">
         <v>0.4712661026140976</v>
       </c>
-      <c r="L551" s="13" t="n">
+      <c r="L551" s="12" t="n">
         <v>-1.932752903666775</v>
       </c>
-      <c r="M551" s="11" t="inlineStr">
+      <c r="M551" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -25647,45 +25644,45 @@
       <c r="M552" t="inlineStr"/>
     </row>
     <row r="553">
-      <c r="A553" s="11" t="inlineStr">
+      <c r="A553" s="8" t="inlineStr">
         <is>
           <t>R0552</t>
         </is>
       </c>
-      <c r="B553" s="11" t="inlineStr">
+      <c r="B553" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C553" s="11" t="inlineStr"/>
-      <c r="D553" s="12" t="n">
+      <c r="C553" s="8" t="inlineStr"/>
+      <c r="D553" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="E553" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F553" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G553" s="13" t="n">
+      <c r="E553" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F553" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G553" s="12" t="n">
         <v>0.263375923455839</v>
       </c>
-      <c r="H553" s="13" t="n">
+      <c r="H553" s="12" t="n">
         <v>0.5270972683902927</v>
       </c>
-      <c r="I553" s="13" t="n">
+      <c r="I553" s="12" t="n">
         <v>1.468363960881694</v>
       </c>
-      <c r="J553" s="13" t="n">
+      <c r="J553" s="12" t="n">
         <v>1.763086088323512</v>
       </c>
-      <c r="K553" s="13" t="n">
+      <c r="K553" s="12" t="n">
         <v>1.537219516574116</v>
       </c>
-      <c r="L553" s="13" t="n">
+      <c r="L553" s="12" t="n">
         <v>1.490580249925609</v>
       </c>
-      <c r="M553" s="11" t="inlineStr">
+      <c r="M553" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -26020,90 +26017,90 @@
       <c r="M561" t="inlineStr"/>
     </row>
     <row r="562">
-      <c r="A562" s="11" t="inlineStr">
+      <c r="A562" s="8" t="inlineStr">
         <is>
           <t>R0561</t>
         </is>
       </c>
-      <c r="B562" s="11" t="inlineStr">
+      <c r="B562" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C562" s="11" t="inlineStr"/>
-      <c r="D562" s="12" t="n">
+      <c r="C562" s="8" t="inlineStr"/>
+      <c r="D562" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E562" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F562" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G562" s="13" t="n">
+      <c r="E562" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F562" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G562" s="12" t="n">
         <v>-1.150656487421848</v>
       </c>
-      <c r="H562" s="13" t="n">
+      <c r="H562" s="12" t="n">
         <v>0.5556231849011074</v>
       </c>
-      <c r="I562" s="13" t="n">
+      <c r="I562" s="12" t="n">
         <v>1.056016249620451</v>
       </c>
-      <c r="J562" s="13" t="n">
+      <c r="J562" s="12" t="n">
         <v>0.3006802104086136</v>
       </c>
-      <c r="K562" s="13" t="n">
+      <c r="K562" s="12" t="n">
         <v>1.664641142447482</v>
       </c>
-      <c r="L562" s="13" t="n">
+      <c r="L562" s="12" t="n">
         <v>1.253143096856902</v>
       </c>
-      <c r="M562" s="11" t="inlineStr">
+      <c r="M562" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="11" t="inlineStr">
+      <c r="A563" s="8" t="inlineStr">
         <is>
           <t>R0562</t>
         </is>
       </c>
-      <c r="B563" s="11" t="inlineStr">
+      <c r="B563" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C563" s="11" t="inlineStr"/>
-      <c r="D563" s="12" t="n">
+      <c r="C563" s="8" t="inlineStr"/>
+      <c r="D563" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E563" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F563" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G563" s="13" t="n">
+      <c r="E563" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F563" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G563" s="12" t="n">
         <v>2.760917199912849</v>
       </c>
-      <c r="H563" s="13" t="n">
+      <c r="H563" s="12" t="n">
         <v>0.7976863048334485</v>
       </c>
-      <c r="I563" s="13" t="n">
+      <c r="I563" s="12" t="n">
         <v>0.7097703262038293</v>
       </c>
-      <c r="J563" s="13" t="n">
+      <c r="J563" s="12" t="n">
         <v>-0.4645681083639406</v>
       </c>
-      <c r="K563" s="13" t="n">
+      <c r="K563" s="12" t="n">
         <v>0.3040979978261295</v>
       </c>
-      <c r="L563" s="13" t="n">
+      <c r="L563" s="12" t="n">
         <v>-0.3440075129597683</v>
       </c>
-      <c r="M563" s="11" t="inlineStr">
+      <c r="M563" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -26274,45 +26271,45 @@
       <c r="M567" t="inlineStr"/>
     </row>
     <row r="568">
-      <c r="A568" s="11" t="inlineStr">
+      <c r="A568" s="8" t="inlineStr">
         <is>
           <t>R0567</t>
         </is>
       </c>
-      <c r="B568" s="11" t="inlineStr">
+      <c r="B568" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C568" s="11" t="inlineStr"/>
-      <c r="D568" s="12" t="n">
+      <c r="C568" s="8" t="inlineStr"/>
+      <c r="D568" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E568" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F568" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G568" s="13" t="n">
+      <c r="E568" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F568" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G568" s="12" t="n">
         <v>1.313359140854509</v>
       </c>
-      <c r="H568" s="13" t="n">
+      <c r="H568" s="12" t="n">
         <v>0.5989503863804679</v>
       </c>
-      <c r="I568" s="13" t="n">
+      <c r="I568" s="12" t="n">
         <v>0.6699618145352485</v>
       </c>
-      <c r="J568" s="13" t="n">
+      <c r="J568" s="12" t="n">
         <v>-1.121171047055982</v>
       </c>
-      <c r="K568" s="13" t="n">
+      <c r="K568" s="12" t="n">
         <v>0.4782342723802041</v>
       </c>
-      <c r="L568" s="13" t="n">
+      <c r="L568" s="12" t="n">
         <v>-0.9314566655880164</v>
       </c>
-      <c r="M568" s="11" t="inlineStr">
+      <c r="M568" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -26647,45 +26644,45 @@
       <c r="M576" t="inlineStr"/>
     </row>
     <row r="577">
-      <c r="A577" s="11" t="inlineStr">
+      <c r="A577" s="8" t="inlineStr">
         <is>
           <t>R0576</t>
         </is>
       </c>
-      <c r="B577" s="11" t="inlineStr">
+      <c r="B577" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C577" s="11" t="inlineStr"/>
-      <c r="D577" s="12" t="n">
+      <c r="C577" s="8" t="inlineStr"/>
+      <c r="D577" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E577" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F577" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G577" s="13" t="n">
+      <c r="E577" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F577" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G577" s="12" t="n">
         <v>1.140817678674626</v>
       </c>
-      <c r="H577" s="13" t="n">
+      <c r="H577" s="12" t="n">
         <v>0.5618791360218677</v>
       </c>
-      <c r="I577" s="13" t="n">
+      <c r="I577" s="12" t="n">
         <v>0.4534248371430461</v>
       </c>
-      <c r="J577" s="13" t="n">
+      <c r="J577" s="12" t="n">
         <v>-2.455182997961534</v>
       </c>
-      <c r="K577" s="13" t="n">
+      <c r="K577" s="12" t="n">
         <v>0.3451120904016781</v>
       </c>
-      <c r="L577" s="13" t="n">
+      <c r="L577" s="12" t="n">
         <v>-1.622682303580278</v>
       </c>
-      <c r="M577" s="11" t="inlineStr">
+      <c r="M577" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -26733,45 +26730,45 @@
       <c r="M578" t="inlineStr"/>
     </row>
     <row r="579">
-      <c r="A579" s="11" t="inlineStr">
+      <c r="A579" s="8" t="inlineStr">
         <is>
           <t>R0578</t>
         </is>
       </c>
-      <c r="B579" s="11" t="inlineStr">
+      <c r="B579" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C579" s="11" t="inlineStr"/>
-      <c r="D579" s="12" t="n">
+      <c r="C579" s="8" t="inlineStr"/>
+      <c r="D579" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="E579" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F579" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G579" s="13" t="n">
+      <c r="E579" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F579" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G579" s="12" t="n">
         <v>0.5444335812258353</v>
       </c>
-      <c r="H579" s="13" t="n">
+      <c r="H579" s="12" t="n">
         <v>0.5338858410554059</v>
       </c>
-      <c r="I579" s="13" t="n">
+      <c r="I579" s="12" t="n">
         <v>1.606435262347781</v>
       </c>
-      <c r="J579" s="13" t="n">
+      <c r="J579" s="12" t="n">
         <v>2.12651553463419</v>
       </c>
-      <c r="K579" s="13" t="n">
+      <c r="K579" s="12" t="n">
         <v>2.176823072576567</v>
       </c>
-      <c r="L579" s="13" t="n">
+      <c r="L579" s="12" t="n">
         <v>2.535483034374185</v>
       </c>
-      <c r="M579" s="11" t="inlineStr">
+      <c r="M579" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -26860,45 +26857,45 @@
       <c r="M581" t="inlineStr"/>
     </row>
     <row r="582">
-      <c r="A582" s="11" t="inlineStr">
+      <c r="A582" s="8" t="inlineStr">
         <is>
           <t>R0581</t>
         </is>
       </c>
-      <c r="B582" s="11" t="inlineStr">
+      <c r="B582" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C582" s="11" t="inlineStr"/>
-      <c r="D582" s="12" t="n">
+      <c r="C582" s="8" t="inlineStr"/>
+      <c r="D582" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E582" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F582" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G582" s="13" t="n">
+      <c r="E582" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F582" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G582" s="12" t="n">
         <v>-0.1560023310472355</v>
       </c>
-      <c r="H582" s="13" t="n">
+      <c r="H582" s="12" t="n">
         <v>0.543157596885137</v>
       </c>
-      <c r="I582" s="13" t="n">
+      <c r="I582" s="12" t="n">
         <v>1.954253829294117</v>
       </c>
-      <c r="J582" s="13" t="n">
+      <c r="J582" s="12" t="n">
         <v>3.043454326825091</v>
       </c>
-      <c r="K582" s="13" t="n">
+      <c r="K582" s="12" t="n">
         <v>2.184739930631988</v>
       </c>
-      <c r="L582" s="13" t="n">
+      <c r="L582" s="12" t="n">
         <v>2.681916846622074</v>
       </c>
-      <c r="M582" s="11" t="inlineStr">
+      <c r="M582" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -26987,45 +26984,45 @@
       <c r="M584" t="inlineStr"/>
     </row>
     <row r="585">
-      <c r="A585" s="11" t="inlineStr">
+      <c r="A585" s="8" t="inlineStr">
         <is>
           <t>R0584</t>
         </is>
       </c>
-      <c r="B585" s="11" t="inlineStr">
+      <c r="B585" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="C585" s="11" t="inlineStr"/>
-      <c r="D585" s="12" t="n">
+      <c r="C585" s="8" t="inlineStr"/>
+      <c r="D585" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E585" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F585" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G585" s="13" t="n">
+      <c r="E585" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F585" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G585" s="12" t="n">
         <v>1.46967040698167</v>
       </c>
-      <c r="H585" s="13" t="n">
+      <c r="H585" s="12" t="n">
         <v>0.5865582715673844</v>
       </c>
-      <c r="I585" s="13" t="n">
+      <c r="I585" s="12" t="n">
         <v>1.758034660499214</v>
       </c>
-      <c r="J585" s="13" t="n">
+      <c r="J585" s="12" t="n">
         <v>2.228937600661207</v>
       </c>
-      <c r="K585" s="13" t="n">
+      <c r="K585" s="12" t="n">
         <v>2.836771210354028</v>
       </c>
-      <c r="L585" s="13" t="n">
+      <c r="L585" s="12" t="n">
         <v>2.266228537964592</v>
       </c>
-      <c r="M585" s="11" t="inlineStr">
+      <c r="M585" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -27606,90 +27603,90 @@
       <c r="M599" t="inlineStr"/>
     </row>
     <row r="600">
-      <c r="A600" s="11" t="inlineStr">
+      <c r="A600" s="8" t="inlineStr">
         <is>
           <t>R0599</t>
         </is>
       </c>
-      <c r="B600" s="11" t="inlineStr">
+      <c r="B600" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C600" s="11" t="inlineStr"/>
-      <c r="D600" s="12" t="n">
+      <c r="C600" s="8" t="inlineStr"/>
+      <c r="D600" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="E600" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F600" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G600" s="13" t="n">
+      <c r="E600" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F600" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G600" s="12" t="n">
         <v>-0.5655280740349017</v>
       </c>
-      <c r="H600" s="13" t="n">
+      <c r="H600" s="12" t="n">
         <v>0.5301142963227143</v>
       </c>
-      <c r="I600" s="13" t="n">
+      <c r="I600" s="12" t="n">
         <v>1.316567194244199</v>
       </c>
-      <c r="J600" s="13" t="n">
+      <c r="J600" s="12" t="n">
         <v>1.295795275810864</v>
       </c>
-      <c r="K600" s="13" t="n">
+      <c r="K600" s="12" t="n">
         <v>1.67378810014798</v>
       </c>
-      <c r="L600" s="13" t="n">
+      <c r="L600" s="12" t="n">
         <v>1.615993987711407</v>
       </c>
-      <c r="M600" s="11" t="inlineStr">
+      <c r="M600" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="11" t="inlineStr">
+      <c r="A601" s="8" t="inlineStr">
         <is>
           <t>R0600</t>
         </is>
       </c>
-      <c r="B601" s="11" t="inlineStr">
+      <c r="B601" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C601" s="11" t="inlineStr"/>
-      <c r="D601" s="12" t="n">
+      <c r="C601" s="8" t="inlineStr"/>
+      <c r="D601" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E601" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F601" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G601" s="13" t="n">
+      <c r="E601" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F601" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G601" s="12" t="n">
         <v>1.460672327105766</v>
       </c>
-      <c r="H601" s="13" t="n">
+      <c r="H601" s="12" t="n">
         <v>0.5883596787246832</v>
       </c>
-      <c r="I601" s="13" t="n">
+      <c r="I601" s="12" t="n">
         <v>1.155504970074617</v>
       </c>
-      <c r="J601" s="13" t="n">
+      <c r="J601" s="12" t="n">
         <v>0.609559753526279</v>
       </c>
-      <c r="K601" s="13" t="n">
+      <c r="K601" s="12" t="n">
         <v>1.895481967406611</v>
       </c>
-      <c r="L601" s="13" t="n">
+      <c r="L601" s="12" t="n">
         <v>1.479649135645481</v>
       </c>
-      <c r="M601" s="11" t="inlineStr">
+      <c r="M601" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -27721,14 +27718,14 @@
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Butir</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
@@ -27763,17 +27760,17 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>Kontras DIF</t>
+          <t>DIF Contrast</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>SE gabungan</t>
+          <t>Joint SE</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>t Welch</t>
+          <t>Welch t</t>
         </is>
       </c>
       <c r="K1" s="4" t="inlineStr">
@@ -27788,12 +27785,12 @@
       </c>
       <c r="M1" s="4" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>ETS Category</t>
         </is>
       </c>
       <c r="N1" s="4" t="inlineStr">
         <is>
-          <t>DIF</t>
+          <t>DIF Flag</t>
         </is>
       </c>
     </row>
@@ -27833,7 +27830,7 @@
       <c r="K2" s="9" t="n">
         <v>585.8595169764216</v>
       </c>
-      <c r="L2" s="17" t="n">
+      <c r="L2" s="16" t="n">
         <v>0.7034706500785549</v>
       </c>
       <c r="M2" t="inlineStr">
@@ -27879,7 +27876,7 @@
       <c r="K3" s="9" t="n">
         <v>579.9658741617991</v>
       </c>
-      <c r="L3" s="17" t="n">
+      <c r="L3" s="16" t="n">
         <v>0.2587472560238696</v>
       </c>
       <c r="M3" t="inlineStr">
@@ -27925,7 +27922,7 @@
       <c r="K4" s="9" t="n">
         <v>587.3126760413154</v>
       </c>
-      <c r="L4" s="17" t="n">
+      <c r="L4" s="16" t="n">
         <v>0.8037084704936034</v>
       </c>
       <c r="M4" t="inlineStr">
@@ -27971,7 +27968,7 @@
       <c r="K5" s="9" t="n">
         <v>558.8495484682518</v>
       </c>
-      <c r="L5" s="17" t="n">
+      <c r="L5" s="16" t="n">
         <v>0.05102698297283736</v>
       </c>
       <c r="M5" t="inlineStr">
@@ -28017,7 +28014,7 @@
       <c r="K6" s="9" t="n">
         <v>577.6074768244958</v>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="L6" s="16" t="n">
         <v>0.9750301718200286</v>
       </c>
       <c r="M6" t="inlineStr">
@@ -28063,7 +28060,7 @@
       <c r="K7" s="9" t="n">
         <v>581.9848477211528</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="16" t="n">
         <v>0.2618209982061438</v>
       </c>
       <c r="M7" t="inlineStr">
@@ -28109,7 +28106,7 @@
       <c r="K8" s="9" t="n">
         <v>577.1679578559042</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="16" t="n">
         <v>0.5374538545035041</v>
       </c>
       <c r="M8" t="inlineStr">
@@ -28155,7 +28152,7 @@
       <c r="K9" s="9" t="n">
         <v>582.702035462056</v>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="L9" s="16" t="n">
         <v>0.08398616772262213</v>
       </c>
       <c r="M9" t="inlineStr">
@@ -28201,7 +28198,7 @@
       <c r="K10" s="9" t="n">
         <v>579.9034263757536</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="16" t="n">
         <v>0.7196275486012725</v>
       </c>
       <c r="M10" t="inlineStr">
@@ -28247,7 +28244,7 @@
       <c r="K11" s="9" t="n">
         <v>586.3452341153112</v>
       </c>
-      <c r="L11" s="17" t="n">
+      <c r="L11" s="16" t="n">
         <v>0.171927463121865</v>
       </c>
       <c r="M11" t="inlineStr">
@@ -28293,7 +28290,7 @@
       <c r="K12" s="9" t="n">
         <v>582.2396485014839</v>
       </c>
-      <c r="L12" s="17" t="n">
+      <c r="L12" s="16" t="n">
         <v>0.2752556602465498</v>
       </c>
       <c r="M12" t="inlineStr">
@@ -28304,50 +28301,50 @@
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="12" t="n">
         <v>1.163531884531916</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="12" t="n">
         <v>0.1315863731569857</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="8" t="n">
         <v>303</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="12" t="n">
         <v>2.134909293230125</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="12" t="n">
         <v>0.1653446271726755</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="8" t="n">
         <v>287</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="12" t="n">
         <v>-0.9713774086982094</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="12" t="n">
         <v>0.2113145033722971</v>
       </c>
-      <c r="J13" s="13" t="n">
+      <c r="J13" s="12" t="n">
         <v>-4.596832650841868</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="K13" s="11" t="n">
         <v>552.9459647076225</v>
       </c>
-      <c r="L13" s="18" t="n">
+      <c r="L13" s="17" t="n">
         <v>5.320154608111243e-06</v>
       </c>
-      <c r="M13" s="11" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N13" s="8" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
@@ -28389,7 +28386,7 @@
       <c r="K14" s="9" t="n">
         <v>577.5898439643163</v>
       </c>
-      <c r="L14" s="17" t="n">
+      <c r="L14" s="16" t="n">
         <v>0.7390787606377087</v>
       </c>
       <c r="M14" t="inlineStr">
@@ -28435,7 +28432,7 @@
       <c r="K15" s="9" t="n">
         <v>576.6615633834839</v>
       </c>
-      <c r="L15" s="17" t="n">
+      <c r="L15" s="16" t="n">
         <v>0.3216610479195421</v>
       </c>
       <c r="M15" t="inlineStr">
@@ -28481,7 +28478,7 @@
       <c r="K16" s="9" t="n">
         <v>585.8606032650911</v>
       </c>
-      <c r="L16" s="17" t="n">
+      <c r="L16" s="16" t="n">
         <v>0.06521707288907871</v>
       </c>
       <c r="M16" t="inlineStr">
@@ -28527,7 +28524,7 @@
       <c r="K17" s="9" t="n">
         <v>578.2117323473155</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="16" t="n">
         <v>0.9826960453585361</v>
       </c>
       <c r="M17" t="inlineStr">
@@ -28573,7 +28570,7 @@
       <c r="K18" s="9" t="n">
         <v>583.5172330537044</v>
       </c>
-      <c r="L18" s="17" t="n">
+      <c r="L18" s="16" t="n">
         <v>0.7978167911079208</v>
       </c>
       <c r="M18" t="inlineStr">
@@ -28619,7 +28616,7 @@
       <c r="K19" s="9" t="n">
         <v>583.8790760693972</v>
       </c>
-      <c r="L19" s="17" t="n">
+      <c r="L19" s="16" t="n">
         <v>0.03732821609139867</v>
       </c>
       <c r="M19" t="inlineStr">
@@ -28665,7 +28662,7 @@
       <c r="K20" s="9" t="n">
         <v>577.4372075332402</v>
       </c>
-      <c r="L20" s="17" t="n">
+      <c r="L20" s="16" t="n">
         <v>0.3704785360920758</v>
       </c>
       <c r="M20" t="inlineStr">
@@ -28711,7 +28708,7 @@
       <c r="K21" s="9" t="n">
         <v>588.9042408622296</v>
       </c>
-      <c r="L21" s="17" t="n">
+      <c r="L21" s="16" t="n">
         <v>0.3250160815796769</v>
       </c>
       <c r="M21" t="inlineStr">
@@ -28737,13 +28734,13 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Butir</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
@@ -28753,7 +28750,7 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Loading kontras 1</t>
+          <t>First Contrast Loading</t>
         </is>
       </c>
     </row>
@@ -30492,21 +30489,21 @@
   <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Butir A</t>
+          <t>Item A</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Butir B</t>
+          <t>Item B</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
@@ -30516,7 +30513,7 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Q3 relatif</t>
+          <t>Relative Q3</t>
         </is>
       </c>
     </row>
@@ -30558,7 +30555,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3 responden memiliki skor ekstrem (0 skor minimum, 3 skor maksimum). Mereka tidak ikut estimasi parameter dan diberi measure dengan penyesuaian skor 0,3 poin.</t>
+          <t>3 person memiliki extreme score (0 minimum, 3 maksimum). Mereka tidak ikut estimasi parameter dan diberi measure dengan penyesuaian skor 0,3 poin.</t>
         </is>
       </c>
     </row>
@@ -30570,7 +30567,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Estimasi konvergen setelah 5 iterasi.</t>
+          <t>Estimasi JMLE konvergen setelah 5 iterasi.</t>
         </is>
       </c>
     </row>
@@ -30582,7 +30579,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Measure item dan threshold dikoreksi bias JMLE dengan faktor (L-1)/L = 0.9500 (L = 20 item). Statistik fit dihitung dari estimasi sebelum koreksi.</t>
+          <t>Item measure dan threshold dikoreksi dari JMLE bias dengan faktor (L-1)/L = 0.9500 (L = 20 item). Statistik fit dihitung dari estimasi sebelum koreksi.</t>
         </is>
       </c>
     </row>
@@ -30601,7 +30598,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -30613,12 +30610,12 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Perubahan maks (logit)</t>
+          <t>Max logit change</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Residual skor maks</t>
+          <t>Max score residual</t>
         </is>
       </c>
     </row>
@@ -30626,10 +30623,10 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="n">
+      <c r="B2" s="18" t="n">
         <v>0.09349604064959438</v>
       </c>
-      <c r="C2" s="19" t="n">
+      <c r="C2" s="18" t="n">
         <v>0.3287095001044955</v>
       </c>
     </row>
@@ -30637,10 +30634,10 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="n">
+      <c r="B3" s="18" t="n">
         <v>0.05735326646733307</v>
       </c>
-      <c r="C3" s="19" t="n">
+      <c r="C3" s="18" t="n">
         <v>0.07378584579936343</v>
       </c>
     </row>
@@ -30648,10 +30645,10 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="n">
+      <c r="B4" s="18" t="n">
         <v>0.01253570331108866</v>
       </c>
-      <c r="C4" s="19" t="n">
+      <c r="C4" s="18" t="n">
         <v>0.01357742716366206</v>
       </c>
     </row>
@@ -30659,10 +30656,10 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="18" t="n">
         <v>0.002182411125626338</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="18" t="n">
         <v>0.002450397141032401</v>
       </c>
     </row>
@@ -30670,10 +30667,10 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="18" t="n">
         <v>0.0003874465612763167</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="18" t="n">
         <v>0.0004417998636600529</v>
       </c>
     </row>
